--- a/EGSA2025_short_loan.xlsx
+++ b/EGSA2025_short_loan.xlsx
@@ -5,92 +5,87 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\walfaanaam\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\walfaanaam\Desktop\EGSA_short_term\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="10044"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="EGSA2025_short_loan" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-  </extLst>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="20">
+  <si>
+    <t>loan_id</t>
+  </si>
+  <si>
+    <t>business_date</t>
+  </si>
+  <si>
+    <t>id</t>
+  </si>
+  <si>
+    <t>loan_type</t>
+  </si>
+  <si>
+    <t>disbursed_amount</t>
+  </si>
+  <si>
+    <t>interest_rate</t>
+  </si>
+  <si>
+    <t>interest_amount</t>
+  </si>
+  <si>
+    <t>collection_amount</t>
+  </si>
+  <si>
+    <t>from_account</t>
+  </si>
+  <si>
+    <t>to_account</t>
+  </si>
+  <si>
+    <t>due_date</t>
+  </si>
+  <si>
+    <t>Phone_no</t>
+  </si>
+  <si>
+    <t>status</t>
+  </si>
+  <si>
+    <t>level_3</t>
+  </si>
+  <si>
+    <t>completed</t>
+  </si>
+  <si>
+    <t>level_2</t>
+  </si>
+  <si>
+    <t>level_1</t>
+  </si>
+  <si>
+    <t>level_4</t>
+  </si>
   <si>
     <t>in progress</t>
   </si>
   <si>
     <t>level_6</t>
-  </si>
-  <si>
-    <t>level_4</t>
-  </si>
-  <si>
-    <t>completed</t>
-  </si>
-  <si>
-    <t>level_2</t>
-  </si>
-  <si>
-    <t>level_1</t>
-  </si>
-  <si>
-    <t>level_3</t>
-  </si>
-  <si>
-    <t>status</t>
-  </si>
-  <si>
-    <t>Phone_no</t>
-  </si>
-  <si>
-    <t>due_date</t>
-  </si>
-  <si>
-    <t>to_account</t>
-  </si>
-  <si>
-    <t>from_account</t>
-  </si>
-  <si>
-    <t>collection_amount</t>
-  </si>
-  <si>
-    <t>interest_amount</t>
-  </si>
-  <si>
-    <t>interest_rate</t>
-  </si>
-  <si>
-    <t>disbursed_amount</t>
-  </si>
-  <si>
-    <t>loan_type</t>
-  </si>
-  <si>
-    <t>id</t>
-  </si>
-  <si>
-    <t>business_date</t>
-  </si>
-  <si>
-    <t>loan_id</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -98,16 +93,316 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Calibri Light"/>
+      <family val="2"/>
+      <scheme val="major"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -115,17 +410,206 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="42">
+    <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
+    <cellStyle name="20% - Accent2" xfId="23" builtinId="34" customBuiltin="1"/>
+    <cellStyle name="20% - Accent3" xfId="27" builtinId="38" customBuiltin="1"/>
+    <cellStyle name="20% - Accent4" xfId="31" builtinId="42" customBuiltin="1"/>
+    <cellStyle name="20% - Accent5" xfId="35" builtinId="46" customBuiltin="1"/>
+    <cellStyle name="20% - Accent6" xfId="39" builtinId="50" customBuiltin="1"/>
+    <cellStyle name="40% - Accent1" xfId="20" builtinId="31" customBuiltin="1"/>
+    <cellStyle name="40% - Accent2" xfId="24" builtinId="35" customBuiltin="1"/>
+    <cellStyle name="40% - Accent3" xfId="28" builtinId="39" customBuiltin="1"/>
+    <cellStyle name="40% - Accent4" xfId="32" builtinId="43" customBuiltin="1"/>
+    <cellStyle name="40% - Accent5" xfId="36" builtinId="47" customBuiltin="1"/>
+    <cellStyle name="40% - Accent6" xfId="40" builtinId="51" customBuiltin="1"/>
+    <cellStyle name="60% - Accent1" xfId="21" builtinId="32" customBuiltin="1"/>
+    <cellStyle name="60% - Accent2" xfId="25" builtinId="36" customBuiltin="1"/>
+    <cellStyle name="60% - Accent3" xfId="29" builtinId="40" customBuiltin="1"/>
+    <cellStyle name="60% - Accent4" xfId="33" builtinId="44" customBuiltin="1"/>
+    <cellStyle name="60% - Accent5" xfId="37" builtinId="48" customBuiltin="1"/>
+    <cellStyle name="60% - Accent6" xfId="41" builtinId="52" customBuiltin="1"/>
+    <cellStyle name="Accent1" xfId="18" builtinId="29" customBuiltin="1"/>
+    <cellStyle name="Accent2" xfId="22" builtinId="33" customBuiltin="1"/>
+    <cellStyle name="Accent3" xfId="26" builtinId="37" customBuiltin="1"/>
+    <cellStyle name="Accent4" xfId="30" builtinId="41" customBuiltin="1"/>
+    <cellStyle name="Accent5" xfId="34" builtinId="45" customBuiltin="1"/>
+    <cellStyle name="Accent6" xfId="38" builtinId="49" customBuiltin="1"/>
+    <cellStyle name="Bad" xfId="7" builtinId="27" customBuiltin="1"/>
+    <cellStyle name="Calculation" xfId="11" builtinId="22" customBuiltin="1"/>
+    <cellStyle name="Check Cell" xfId="13" builtinId="23" customBuiltin="1"/>
+    <cellStyle name="Explanatory Text" xfId="16" builtinId="53" customBuiltin="1"/>
+    <cellStyle name="Good" xfId="6" builtinId="26" customBuiltin="1"/>
+    <cellStyle name="Heading 1" xfId="2" builtinId="16" customBuiltin="1"/>
+    <cellStyle name="Heading 2" xfId="3" builtinId="17" customBuiltin="1"/>
+    <cellStyle name="Heading 3" xfId="4" builtinId="18" customBuiltin="1"/>
+    <cellStyle name="Heading 4" xfId="5" builtinId="19" customBuiltin="1"/>
+    <cellStyle name="Input" xfId="9" builtinId="20" customBuiltin="1"/>
+    <cellStyle name="Linked Cell" xfId="12" builtinId="24" customBuiltin="1"/>
+    <cellStyle name="Neutral" xfId="8" builtinId="28" customBuiltin="1"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Note" xfId="15" builtinId="10" customBuiltin="1"/>
+    <cellStyle name="Output" xfId="10" builtinId="21" customBuiltin="1"/>
+    <cellStyle name="Title" xfId="1" builtinId="15" customBuiltin="1"/>
+    <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
+    <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -407,64 +891,65 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.109375" style="2" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.5546875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.109375" style="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F1" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="G1" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" t="s">
         <v>12</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="K1" t="s">
-        <v>9</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="M1" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" s="2">
+      <c r="B2" s="1">
         <v>46062</v>
       </c>
       <c r="C2">
         <v>1010</v>
       </c>
       <c r="D2" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E2">
         <v>9000</v>
@@ -478,34 +963,34 @@
       <c r="H2">
         <v>10000</v>
       </c>
-      <c r="I2" s="1">
+      <c r="I2" s="2">
         <v>1000724673337</v>
       </c>
-      <c r="J2" s="1">
+      <c r="J2" s="2">
         <v>1000289318236</v>
       </c>
-      <c r="K2" s="2">
+      <c r="K2" s="1">
         <v>46092</v>
       </c>
-      <c r="L2" s="1">
+      <c r="L2" s="2">
         <v>251926757080</v>
       </c>
       <c r="M2" t="s">
-        <v>3</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
-      <c r="B3" s="2">
+      <c r="B3" s="1">
         <v>46062</v>
       </c>
       <c r="C3">
         <v>1002</v>
       </c>
       <c r="D3" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="E3">
         <v>4750</v>
@@ -519,34 +1004,34 @@
       <c r="H3">
         <v>5000</v>
       </c>
-      <c r="I3" s="1">
+      <c r="I3" s="2">
         <v>1000724673337</v>
       </c>
-      <c r="J3" s="1">
+      <c r="J3" s="2">
         <v>1000177190024</v>
       </c>
-      <c r="K3" s="2">
+      <c r="K3" s="1">
         <v>46077</v>
       </c>
-      <c r="L3" s="1">
+      <c r="L3" s="2">
         <v>251912861288</v>
       </c>
       <c r="M3" t="s">
-        <v>3</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
-      <c r="B4" s="2">
+      <c r="B4" s="1">
         <v>46062</v>
       </c>
       <c r="C4">
         <v>1006</v>
       </c>
       <c r="D4" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="E4">
         <v>1900</v>
@@ -560,34 +1045,34 @@
       <c r="H4">
         <v>2000</v>
       </c>
-      <c r="I4" s="1">
+      <c r="I4" s="2">
         <v>1000724673337</v>
       </c>
-      <c r="J4" s="1">
+      <c r="J4" s="2">
         <v>1000272980423</v>
       </c>
-      <c r="K4" s="2">
+      <c r="K4" s="1">
         <v>46069</v>
       </c>
-      <c r="L4" s="1">
+      <c r="L4" s="2">
         <v>251911818685</v>
       </c>
       <c r="M4" t="s">
-        <v>3</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
-      <c r="B5" s="2">
+      <c r="B5" s="1">
         <v>46063</v>
       </c>
       <c r="C5">
         <v>1003</v>
       </c>
       <c r="D5" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="E5">
         <v>12750</v>
@@ -601,34 +1086,34 @@
       <c r="H5">
         <v>15000</v>
       </c>
-      <c r="I5" s="1">
+      <c r="I5" s="2">
         <v>1000724673337</v>
       </c>
-      <c r="J5" s="1">
+      <c r="J5" s="2">
         <v>1000496218101</v>
       </c>
-      <c r="K5" s="2">
-        <v>46123</v>
-      </c>
-      <c r="L5" s="1">
+      <c r="K5" s="1">
+        <v>46115</v>
+      </c>
+      <c r="L5" s="2">
         <v>251977677737</v>
       </c>
       <c r="M5" t="s">
-        <v>0</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
-      <c r="B6" s="2">
+      <c r="B6" s="1">
         <v>46064</v>
       </c>
       <c r="C6">
         <v>1014</v>
       </c>
       <c r="D6" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="E6">
         <v>4750</v>
@@ -642,34 +1127,34 @@
       <c r="H6">
         <v>5000</v>
       </c>
-      <c r="I6" s="1">
+      <c r="I6" s="2">
         <v>1000724673337</v>
       </c>
-      <c r="J6" s="1">
+      <c r="J6" s="2">
         <v>1000378957161</v>
       </c>
-      <c r="K6" s="2">
+      <c r="K6" s="1">
         <v>46079</v>
       </c>
-      <c r="L6" s="1">
+      <c r="L6" s="2">
         <v>251930308503</v>
       </c>
       <c r="M6" t="s">
-        <v>3</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>6</v>
       </c>
-      <c r="B7" s="2">
+      <c r="B7" s="1">
         <v>46079</v>
       </c>
       <c r="C7">
         <v>1002</v>
       </c>
       <c r="D7" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="E7">
         <v>12750</v>
@@ -683,34 +1168,34 @@
       <c r="H7">
         <v>15000</v>
       </c>
-      <c r="I7" s="1">
+      <c r="I7" s="2">
         <v>1000724673337</v>
       </c>
-      <c r="J7" s="1">
+      <c r="J7" s="2">
         <v>1000177190024</v>
       </c>
-      <c r="K7" s="2">
+      <c r="K7" s="1">
         <v>46109</v>
       </c>
-      <c r="L7" s="1">
+      <c r="L7" s="2">
         <v>251912861288</v>
       </c>
       <c r="M7" t="s">
-        <v>3</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>7</v>
       </c>
-      <c r="B8" s="2">
+      <c r="B8" s="1">
         <v>46079</v>
       </c>
       <c r="C8">
         <v>1011</v>
       </c>
       <c r="D8" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="E8">
         <v>12750</v>
@@ -724,34 +1209,34 @@
       <c r="H8">
         <v>15000</v>
       </c>
-      <c r="I8" s="1">
+      <c r="I8" s="2">
         <v>1000724673337</v>
       </c>
-      <c r="J8" s="1">
+      <c r="J8" s="2">
         <v>1000531405424</v>
       </c>
-      <c r="K8" s="2">
+      <c r="K8" s="1">
         <v>46138</v>
       </c>
-      <c r="L8" s="1">
+      <c r="L8" s="2">
         <v>251947763811</v>
       </c>
       <c r="M8" t="s">
-        <v>0</v>
+        <v>18</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>8</v>
       </c>
-      <c r="B9" s="2">
+      <c r="B9" s="1">
         <v>46080</v>
       </c>
       <c r="C9">
         <v>1007</v>
       </c>
       <c r="D9" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="E9">
         <v>12750</v>
@@ -765,34 +1250,34 @@
       <c r="H9">
         <v>15000</v>
       </c>
-      <c r="I9" s="1">
+      <c r="I9" s="2">
         <v>1000724673337</v>
       </c>
-      <c r="J9" s="1">
+      <c r="J9" s="2">
         <v>1000553520502</v>
       </c>
-      <c r="K9" s="2">
+      <c r="K9" s="1">
         <v>46140</v>
       </c>
-      <c r="L9" s="1">
+      <c r="L9" s="2">
         <v>251954846351</v>
       </c>
       <c r="M9" t="s">
-        <v>0</v>
+        <v>18</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>9</v>
       </c>
-      <c r="B10" s="2">
+      <c r="B10" s="1">
         <v>46080</v>
       </c>
       <c r="C10">
         <v>1010</v>
       </c>
       <c r="D10" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="E10">
         <v>12750</v>
@@ -806,34 +1291,34 @@
       <c r="H10">
         <v>15000</v>
       </c>
-      <c r="I10" s="1">
+      <c r="I10" s="2">
         <v>1000724673337</v>
       </c>
-      <c r="J10" s="1">
+      <c r="J10" s="2">
         <v>1000289318236</v>
       </c>
-      <c r="K10" s="2">
+      <c r="K10" s="1">
         <v>46140</v>
       </c>
-      <c r="L10" s="1">
+      <c r="L10" s="2">
         <v>251926757080</v>
       </c>
       <c r="M10" t="s">
-        <v>0</v>
+        <v>18</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>10</v>
       </c>
-      <c r="B11" s="2">
+      <c r="B11" s="1">
         <v>46081</v>
       </c>
       <c r="C11">
         <v>1005</v>
       </c>
       <c r="D11" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="E11">
         <v>12750</v>
@@ -847,34 +1332,34 @@
       <c r="H11">
         <v>15000</v>
       </c>
-      <c r="I11" s="1">
+      <c r="I11" s="2">
         <v>1000724673337</v>
       </c>
-      <c r="J11" s="1">
+      <c r="J11" s="2">
         <v>1000263206022</v>
       </c>
-      <c r="K11" s="2">
+      <c r="K11" s="1">
         <v>46141</v>
       </c>
-      <c r="L11" s="1">
+      <c r="L11" s="2">
         <v>251935869198</v>
       </c>
       <c r="M11" t="s">
-        <v>0</v>
+        <v>18</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>11</v>
       </c>
-      <c r="B12" s="2">
+      <c r="B12" s="1">
         <v>46081</v>
       </c>
       <c r="C12">
         <v>1013</v>
       </c>
       <c r="D12" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="E12">
         <v>12750</v>
@@ -888,34 +1373,34 @@
       <c r="H12">
         <v>15000</v>
       </c>
-      <c r="I12" s="1">
+      <c r="I12" s="2">
         <v>1000724673337</v>
       </c>
-      <c r="J12" s="1">
+      <c r="J12" s="2">
         <v>1000094217214</v>
       </c>
-      <c r="K12" s="2">
+      <c r="K12" s="1">
         <v>46141</v>
       </c>
-      <c r="L12" s="1">
+      <c r="L12" s="2">
         <v>251923151481</v>
       </c>
       <c r="M12" t="s">
-        <v>0</v>
+        <v>18</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>12</v>
       </c>
-      <c r="B13" s="2">
+      <c r="B13" s="1">
         <v>46088</v>
       </c>
       <c r="C13">
         <v>1023</v>
       </c>
       <c r="D13" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="E13">
         <v>12750</v>
@@ -929,34 +1414,34 @@
       <c r="H13">
         <v>15000</v>
       </c>
-      <c r="I13" s="1">
+      <c r="I13" s="2">
         <v>1000727672676</v>
       </c>
-      <c r="J13" s="1">
+      <c r="J13" s="2">
         <v>1000657475649</v>
       </c>
-      <c r="K13" s="2">
+      <c r="K13" s="1">
         <v>46150</v>
       </c>
-      <c r="L13" s="1">
+      <c r="L13" s="2">
         <v>251919159451</v>
       </c>
       <c r="M13" t="s">
-        <v>0</v>
+        <v>18</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>13</v>
       </c>
-      <c r="B14" s="2">
+      <c r="B14" s="1">
         <v>46104</v>
       </c>
       <c r="C14">
         <v>1017</v>
       </c>
       <c r="D14" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="E14">
         <v>12750</v>
@@ -970,34 +1455,34 @@
       <c r="H14">
         <v>15000</v>
       </c>
-      <c r="I14" s="1">
+      <c r="I14" s="2">
         <v>1000724673337</v>
       </c>
-      <c r="J14" s="1">
+      <c r="J14" s="2">
         <v>1000016351087</v>
       </c>
-      <c r="K14" s="2">
+      <c r="K14" s="1">
         <v>46165</v>
       </c>
-      <c r="L14" s="1">
+      <c r="L14" s="2">
         <v>251912356447</v>
       </c>
       <c r="M14" t="s">
-        <v>0</v>
+        <v>18</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>14</v>
       </c>
-      <c r="B15" s="2">
+      <c r="B15" s="1">
         <v>46104</v>
       </c>
       <c r="C15">
         <v>1008</v>
       </c>
       <c r="D15" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="E15">
         <v>12750</v>
@@ -1011,34 +1496,34 @@
       <c r="H15">
         <v>15000</v>
       </c>
-      <c r="I15" s="1">
+      <c r="I15" s="2">
         <v>1000724673337</v>
       </c>
-      <c r="J15" s="1">
+      <c r="J15" s="2">
         <v>1000205376635</v>
       </c>
-      <c r="K15" s="2">
+      <c r="K15" s="1">
         <v>46165</v>
       </c>
-      <c r="L15" s="1">
+      <c r="L15" s="2">
         <v>251922956646</v>
       </c>
       <c r="M15" t="s">
-        <v>0</v>
+        <v>18</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>15</v>
       </c>
-      <c r="B16" s="2">
+      <c r="B16" s="1">
         <v>46104</v>
       </c>
       <c r="C16">
         <v>1006</v>
       </c>
       <c r="D16" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="E16">
         <v>12750</v>
@@ -1052,34 +1537,34 @@
       <c r="H16">
         <v>15000</v>
       </c>
-      <c r="I16" s="1">
+      <c r="I16" s="2">
         <v>1000724673337</v>
       </c>
-      <c r="J16" s="1">
+      <c r="J16" s="2">
         <v>1000272980423</v>
       </c>
-      <c r="K16" s="2">
+      <c r="K16" s="1">
         <v>46165</v>
       </c>
-      <c r="L16" s="1">
+      <c r="L16" s="2">
         <v>251911818685</v>
       </c>
       <c r="M16" t="s">
-        <v>0</v>
+        <v>18</v>
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>16</v>
       </c>
-      <c r="B17" s="2">
+      <c r="B17" s="1">
         <v>46104</v>
       </c>
       <c r="C17">
         <v>1014</v>
       </c>
       <c r="D17" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="E17">
         <v>12750</v>
@@ -1093,34 +1578,34 @@
       <c r="H17">
         <v>15000</v>
       </c>
-      <c r="I17" s="1">
+      <c r="I17" s="2">
         <v>1000724673337</v>
       </c>
-      <c r="J17" s="1">
+      <c r="J17" s="2">
         <v>1000378957161</v>
       </c>
-      <c r="K17" s="2">
+      <c r="K17" s="1">
         <v>46165</v>
       </c>
-      <c r="L17" s="1">
+      <c r="L17" s="2">
         <v>251930308503</v>
       </c>
       <c r="M17" t="s">
-        <v>0</v>
+        <v>18</v>
       </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>17</v>
       </c>
-      <c r="B18" s="2">
+      <c r="B18" s="1">
         <v>46109</v>
       </c>
       <c r="C18">
         <v>1002</v>
       </c>
       <c r="D18" t="s">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="E18">
         <v>85000</v>
@@ -1134,28 +1619,65 @@
       <c r="H18">
         <v>100000</v>
       </c>
-      <c r="I18" s="1">
+      <c r="I18" s="2">
         <v>1000724673337</v>
       </c>
-      <c r="J18" s="1">
+      <c r="J18" s="2">
         <v>1000177190024</v>
       </c>
-      <c r="K18" s="2">
+      <c r="K18" s="1">
         <v>46293</v>
       </c>
-      <c r="L18" s="1">
+      <c r="L18" s="2">
         <v>251912861288</v>
       </c>
       <c r="M18" t="s">
-        <v>0</v>
+        <v>18</v>
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="I19" s="1"/>
-      <c r="J19" s="1"/>
-      <c r="L19" s="1"/>
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19" s="1">
+        <v>46115</v>
+      </c>
+      <c r="C19">
+        <v>1003</v>
+      </c>
+      <c r="D19" t="s">
+        <v>19</v>
+      </c>
+      <c r="E19">
+        <v>85000</v>
+      </c>
+      <c r="F19">
+        <v>15</v>
+      </c>
+      <c r="G19">
+        <v>15000</v>
+      </c>
+      <c r="H19">
+        <v>100000</v>
+      </c>
+      <c r="I19" s="2">
+        <v>1000724673337</v>
+      </c>
+      <c r="J19" s="2">
+        <v>1000496218101</v>
+      </c>
+      <c r="K19" s="1">
+        <v>46298</v>
+      </c>
+      <c r="L19" s="2">
+        <v>251977677737</v>
+      </c>
+      <c r="M19" t="s">
+        <v>18</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/EGSA2025_short_loan.xlsx
+++ b/EGSA2025_short_loan.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\walfaanaam\Desktop\EGSA_short_term\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\walfaanaam\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="20">
   <si>
     <t>loan_id</t>
   </si>
@@ -887,11 +887,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M19"/>
+  <dimension ref="A1:M20"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
+    <col min="1" max="1" width="7" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.44140625" bestFit="1" customWidth="1"/>
     <col min="9" max="10" width="14.109375" style="2" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.5546875" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="13.109375" style="2" bestFit="1" customWidth="1"/>
@@ -1216,13 +1219,13 @@
         <v>1000531405424</v>
       </c>
       <c r="K8" s="1">
-        <v>46138</v>
+        <v>46116</v>
       </c>
       <c r="L8" s="2">
         <v>251947763811</v>
       </c>
       <c r="M8" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.3">
@@ -1673,6 +1676,47 @@
         <v>251977677737</v>
       </c>
       <c r="M19" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20" s="1">
+        <v>46116</v>
+      </c>
+      <c r="C20">
+        <v>1011</v>
+      </c>
+      <c r="D20" t="s">
+        <v>17</v>
+      </c>
+      <c r="E20">
+        <v>21250</v>
+      </c>
+      <c r="F20">
+        <v>15</v>
+      </c>
+      <c r="G20">
+        <v>3750</v>
+      </c>
+      <c r="H20">
+        <v>25000</v>
+      </c>
+      <c r="I20" s="2">
+        <v>1000724673337</v>
+      </c>
+      <c r="J20" s="2">
+        <v>1000531405424</v>
+      </c>
+      <c r="K20" s="1">
+        <v>46176</v>
+      </c>
+      <c r="L20" s="2">
+        <v>251947763811</v>
+      </c>
+      <c r="M20" t="s">
         <v>18</v>
       </c>
     </row>

--- a/EGSA2025_short_loan.xlsx
+++ b/EGSA2025_short_loan.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\walfaanaam\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\walfaanaam\Desktop\general\EGSA_short_term\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="20">
   <si>
     <t>loan_id</t>
   </si>
@@ -562,10 +562,9 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="17" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -887,17 +886,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M20"/>
+  <dimension ref="A1:M21"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="7" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.6640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.44140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9.5546875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.3">
@@ -925,16 +918,16 @@
       <c r="H1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" t="s">
         <v>9</v>
       </c>
       <c r="K1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="L1" t="s">
         <v>11</v>
       </c>
       <c r="M1" t="s">
@@ -966,16 +959,16 @@
       <c r="H2">
         <v>10000</v>
       </c>
-      <c r="I2" s="2">
-        <v>1000724673337</v>
-      </c>
-      <c r="J2" s="2">
+      <c r="I2">
+        <v>1000724673337</v>
+      </c>
+      <c r="J2">
         <v>1000289318236</v>
       </c>
       <c r="K2" s="1">
         <v>46092</v>
       </c>
-      <c r="L2" s="2">
+      <c r="L2">
         <v>251926757080</v>
       </c>
       <c r="M2" t="s">
@@ -1007,16 +1000,16 @@
       <c r="H3">
         <v>5000</v>
       </c>
-      <c r="I3" s="2">
-        <v>1000724673337</v>
-      </c>
-      <c r="J3" s="2">
+      <c r="I3">
+        <v>1000724673337</v>
+      </c>
+      <c r="J3">
         <v>1000177190024</v>
       </c>
       <c r="K3" s="1">
         <v>46077</v>
       </c>
-      <c r="L3" s="2">
+      <c r="L3">
         <v>251912861288</v>
       </c>
       <c r="M3" t="s">
@@ -1048,16 +1041,16 @@
       <c r="H4">
         <v>2000</v>
       </c>
-      <c r="I4" s="2">
-        <v>1000724673337</v>
-      </c>
-      <c r="J4" s="2">
+      <c r="I4">
+        <v>1000724673337</v>
+      </c>
+      <c r="J4">
         <v>1000272980423</v>
       </c>
       <c r="K4" s="1">
         <v>46069</v>
       </c>
-      <c r="L4" s="2">
+      <c r="L4">
         <v>251911818685</v>
       </c>
       <c r="M4" t="s">
@@ -1089,16 +1082,16 @@
       <c r="H5">
         <v>15000</v>
       </c>
-      <c r="I5" s="2">
-        <v>1000724673337</v>
-      </c>
-      <c r="J5" s="2">
+      <c r="I5">
+        <v>1000724673337</v>
+      </c>
+      <c r="J5">
         <v>1000496218101</v>
       </c>
       <c r="K5" s="1">
         <v>46115</v>
       </c>
-      <c r="L5" s="2">
+      <c r="L5">
         <v>251977677737</v>
       </c>
       <c r="M5" t="s">
@@ -1130,16 +1123,16 @@
       <c r="H6">
         <v>5000</v>
       </c>
-      <c r="I6" s="2">
-        <v>1000724673337</v>
-      </c>
-      <c r="J6" s="2">
+      <c r="I6">
+        <v>1000724673337</v>
+      </c>
+      <c r="J6">
         <v>1000378957161</v>
       </c>
       <c r="K6" s="1">
         <v>46079</v>
       </c>
-      <c r="L6" s="2">
+      <c r="L6">
         <v>251930308503</v>
       </c>
       <c r="M6" t="s">
@@ -1171,16 +1164,16 @@
       <c r="H7">
         <v>15000</v>
       </c>
-      <c r="I7" s="2">
-        <v>1000724673337</v>
-      </c>
-      <c r="J7" s="2">
+      <c r="I7">
+        <v>1000724673337</v>
+      </c>
+      <c r="J7">
         <v>1000177190024</v>
       </c>
       <c r="K7" s="1">
         <v>46109</v>
       </c>
-      <c r="L7" s="2">
+      <c r="L7">
         <v>251912861288</v>
       </c>
       <c r="M7" t="s">
@@ -1212,16 +1205,16 @@
       <c r="H8">
         <v>15000</v>
       </c>
-      <c r="I8" s="2">
-        <v>1000724673337</v>
-      </c>
-      <c r="J8" s="2">
+      <c r="I8">
+        <v>1000724673337</v>
+      </c>
+      <c r="J8">
         <v>1000531405424</v>
       </c>
       <c r="K8" s="1">
         <v>46116</v>
       </c>
-      <c r="L8" s="2">
+      <c r="L8">
         <v>251947763811</v>
       </c>
       <c r="M8" t="s">
@@ -1253,16 +1246,16 @@
       <c r="H9">
         <v>15000</v>
       </c>
-      <c r="I9" s="2">
-        <v>1000724673337</v>
-      </c>
-      <c r="J9" s="2">
+      <c r="I9">
+        <v>1000724673337</v>
+      </c>
+      <c r="J9">
         <v>1000553520502</v>
       </c>
       <c r="K9" s="1">
         <v>46140</v>
       </c>
-      <c r="L9" s="2">
+      <c r="L9">
         <v>251954846351</v>
       </c>
       <c r="M9" t="s">
@@ -1294,16 +1287,16 @@
       <c r="H10">
         <v>15000</v>
       </c>
-      <c r="I10" s="2">
-        <v>1000724673337</v>
-      </c>
-      <c r="J10" s="2">
+      <c r="I10">
+        <v>1000724673337</v>
+      </c>
+      <c r="J10">
         <v>1000289318236</v>
       </c>
       <c r="K10" s="1">
         <v>46140</v>
       </c>
-      <c r="L10" s="2">
+      <c r="L10">
         <v>251926757080</v>
       </c>
       <c r="M10" t="s">
@@ -1335,16 +1328,16 @@
       <c r="H11">
         <v>15000</v>
       </c>
-      <c r="I11" s="2">
-        <v>1000724673337</v>
-      </c>
-      <c r="J11" s="2">
+      <c r="I11">
+        <v>1000724673337</v>
+      </c>
+      <c r="J11">
         <v>1000263206022</v>
       </c>
       <c r="K11" s="1">
         <v>46141</v>
       </c>
-      <c r="L11" s="2">
+      <c r="L11">
         <v>251935869198</v>
       </c>
       <c r="M11" t="s">
@@ -1376,16 +1369,16 @@
       <c r="H12">
         <v>15000</v>
       </c>
-      <c r="I12" s="2">
-        <v>1000724673337</v>
-      </c>
-      <c r="J12" s="2">
+      <c r="I12">
+        <v>1000724673337</v>
+      </c>
+      <c r="J12">
         <v>1000094217214</v>
       </c>
       <c r="K12" s="1">
         <v>46141</v>
       </c>
-      <c r="L12" s="2">
+      <c r="L12">
         <v>251923151481</v>
       </c>
       <c r="M12" t="s">
@@ -1417,16 +1410,16 @@
       <c r="H13">
         <v>15000</v>
       </c>
-      <c r="I13" s="2">
+      <c r="I13">
         <v>1000727672676</v>
       </c>
-      <c r="J13" s="2">
+      <c r="J13">
         <v>1000657475649</v>
       </c>
       <c r="K13" s="1">
         <v>46150</v>
       </c>
-      <c r="L13" s="2">
+      <c r="L13">
         <v>251919159451</v>
       </c>
       <c r="M13" t="s">
@@ -1458,16 +1451,16 @@
       <c r="H14">
         <v>15000</v>
       </c>
-      <c r="I14" s="2">
-        <v>1000724673337</v>
-      </c>
-      <c r="J14" s="2">
+      <c r="I14">
+        <v>1000724673337</v>
+      </c>
+      <c r="J14">
         <v>1000016351087</v>
       </c>
       <c r="K14" s="1">
         <v>46165</v>
       </c>
-      <c r="L14" s="2">
+      <c r="L14">
         <v>251912356447</v>
       </c>
       <c r="M14" t="s">
@@ -1499,16 +1492,16 @@
       <c r="H15">
         <v>15000</v>
       </c>
-      <c r="I15" s="2">
-        <v>1000724673337</v>
-      </c>
-      <c r="J15" s="2">
+      <c r="I15">
+        <v>1000724673337</v>
+      </c>
+      <c r="J15">
         <v>1000205376635</v>
       </c>
       <c r="K15" s="1">
         <v>46165</v>
       </c>
-      <c r="L15" s="2">
+      <c r="L15">
         <v>251922956646</v>
       </c>
       <c r="M15" t="s">
@@ -1540,16 +1533,16 @@
       <c r="H16">
         <v>15000</v>
       </c>
-      <c r="I16" s="2">
-        <v>1000724673337</v>
-      </c>
-      <c r="J16" s="2">
+      <c r="I16">
+        <v>1000724673337</v>
+      </c>
+      <c r="J16">
         <v>1000272980423</v>
       </c>
       <c r="K16" s="1">
         <v>46165</v>
       </c>
-      <c r="L16" s="2">
+      <c r="L16">
         <v>251911818685</v>
       </c>
       <c r="M16" t="s">
@@ -1581,16 +1574,16 @@
       <c r="H17">
         <v>15000</v>
       </c>
-      <c r="I17" s="2">
-        <v>1000724673337</v>
-      </c>
-      <c r="J17" s="2">
+      <c r="I17">
+        <v>1000724673337</v>
+      </c>
+      <c r="J17">
         <v>1000378957161</v>
       </c>
       <c r="K17" s="1">
         <v>46165</v>
       </c>
-      <c r="L17" s="2">
+      <c r="L17">
         <v>251930308503</v>
       </c>
       <c r="M17" t="s">
@@ -1622,16 +1615,16 @@
       <c r="H18">
         <v>100000</v>
       </c>
-      <c r="I18" s="2">
-        <v>1000724673337</v>
-      </c>
-      <c r="J18" s="2">
+      <c r="I18">
+        <v>1000724673337</v>
+      </c>
+      <c r="J18">
         <v>1000177190024</v>
       </c>
       <c r="K18" s="1">
         <v>46293</v>
       </c>
-      <c r="L18" s="2">
+      <c r="L18">
         <v>251912861288</v>
       </c>
       <c r="M18" t="s">
@@ -1640,7 +1633,7 @@
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A19">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="B19" s="1">
         <v>46115</v>
@@ -1663,16 +1656,16 @@
       <c r="H19">
         <v>100000</v>
       </c>
-      <c r="I19" s="2">
-        <v>1000724673337</v>
-      </c>
-      <c r="J19" s="2">
+      <c r="I19">
+        <v>1000724673337</v>
+      </c>
+      <c r="J19">
         <v>1000496218101</v>
       </c>
       <c r="K19" s="1">
         <v>46298</v>
       </c>
-      <c r="L19" s="2">
+      <c r="L19">
         <v>251977677737</v>
       </c>
       <c r="M19" t="s">
@@ -1681,7 +1674,7 @@
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A20">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="B20" s="1">
         <v>46116</v>
@@ -1704,24 +1697,64 @@
       <c r="H20">
         <v>25000</v>
       </c>
-      <c r="I20" s="2">
-        <v>1000724673337</v>
-      </c>
-      <c r="J20" s="2">
+      <c r="I20">
+        <v>1000724673337</v>
+      </c>
+      <c r="J20">
         <v>1000531405424</v>
       </c>
       <c r="K20" s="1">
         <v>46176</v>
       </c>
-      <c r="L20" s="2">
+      <c r="L20">
         <v>251947763811</v>
       </c>
       <c r="M20" t="s">
         <v>18</v>
       </c>
     </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A21">
+        <v>28</v>
+      </c>
+      <c r="B21" s="1">
+        <v>46123</v>
+      </c>
+      <c r="C21">
+        <v>1006</v>
+      </c>
+      <c r="D21" t="s">
+        <v>19</v>
+      </c>
+      <c r="E21">
+        <v>85000</v>
+      </c>
+      <c r="F21">
+        <v>15</v>
+      </c>
+      <c r="G21">
+        <v>15000</v>
+      </c>
+      <c r="H21">
+        <v>100000</v>
+      </c>
+      <c r="I21">
+        <v>1000724673337</v>
+      </c>
+      <c r="J21">
+        <v>1000272980423</v>
+      </c>
+      <c r="K21" s="1">
+        <v>46306</v>
+      </c>
+      <c r="L21">
+        <v>251911818685</v>
+      </c>
+      <c r="M21" t="s">
+        <v>18</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/EGSA2025_short_loan.xlsx
+++ b/EGSA2025_short_loan.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="20">
   <si>
     <t>loan_id</t>
   </si>
@@ -562,9 +562,10 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="17" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -886,11 +887,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M21"/>
+  <dimension ref="A1:M22"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.109375" style="2" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15.6640625" style="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.3">
@@ -918,16 +921,16 @@
       <c r="H1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+      <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
       <c r="M1" t="s">
@@ -959,16 +962,16 @@
       <c r="H2">
         <v>10000</v>
       </c>
-      <c r="I2">
-        <v>1000724673337</v>
-      </c>
-      <c r="J2">
+      <c r="I2" s="2">
+        <v>1000724673337</v>
+      </c>
+      <c r="J2" s="2">
         <v>1000289318236</v>
       </c>
       <c r="K2" s="1">
         <v>46092</v>
       </c>
-      <c r="L2">
+      <c r="L2" s="2">
         <v>251926757080</v>
       </c>
       <c r="M2" t="s">
@@ -1000,16 +1003,16 @@
       <c r="H3">
         <v>5000</v>
       </c>
-      <c r="I3">
-        <v>1000724673337</v>
-      </c>
-      <c r="J3">
+      <c r="I3" s="2">
+        <v>1000724673337</v>
+      </c>
+      <c r="J3" s="2">
         <v>1000177190024</v>
       </c>
       <c r="K3" s="1">
         <v>46077</v>
       </c>
-      <c r="L3">
+      <c r="L3" s="2">
         <v>251912861288</v>
       </c>
       <c r="M3" t="s">
@@ -1041,16 +1044,16 @@
       <c r="H4">
         <v>2000</v>
       </c>
-      <c r="I4">
-        <v>1000724673337</v>
-      </c>
-      <c r="J4">
+      <c r="I4" s="2">
+        <v>1000724673337</v>
+      </c>
+      <c r="J4" s="2">
         <v>1000272980423</v>
       </c>
       <c r="K4" s="1">
         <v>46069</v>
       </c>
-      <c r="L4">
+      <c r="L4" s="2">
         <v>251911818685</v>
       </c>
       <c r="M4" t="s">
@@ -1082,16 +1085,16 @@
       <c r="H5">
         <v>15000</v>
       </c>
-      <c r="I5">
-        <v>1000724673337</v>
-      </c>
-      <c r="J5">
+      <c r="I5" s="2">
+        <v>1000724673337</v>
+      </c>
+      <c r="J5" s="2">
         <v>1000496218101</v>
       </c>
       <c r="K5" s="1">
         <v>46115</v>
       </c>
-      <c r="L5">
+      <c r="L5" s="2">
         <v>251977677737</v>
       </c>
       <c r="M5" t="s">
@@ -1123,16 +1126,16 @@
       <c r="H6">
         <v>5000</v>
       </c>
-      <c r="I6">
-        <v>1000724673337</v>
-      </c>
-      <c r="J6">
+      <c r="I6" s="2">
+        <v>1000724673337</v>
+      </c>
+      <c r="J6" s="2">
         <v>1000378957161</v>
       </c>
       <c r="K6" s="1">
         <v>46079</v>
       </c>
-      <c r="L6">
+      <c r="L6" s="2">
         <v>251930308503</v>
       </c>
       <c r="M6" t="s">
@@ -1164,16 +1167,16 @@
       <c r="H7">
         <v>15000</v>
       </c>
-      <c r="I7">
-        <v>1000724673337</v>
-      </c>
-      <c r="J7">
+      <c r="I7" s="2">
+        <v>1000724673337</v>
+      </c>
+      <c r="J7" s="2">
         <v>1000177190024</v>
       </c>
       <c r="K7" s="1">
         <v>46109</v>
       </c>
-      <c r="L7">
+      <c r="L7" s="2">
         <v>251912861288</v>
       </c>
       <c r="M7" t="s">
@@ -1205,16 +1208,16 @@
       <c r="H8">
         <v>15000</v>
       </c>
-      <c r="I8">
-        <v>1000724673337</v>
-      </c>
-      <c r="J8">
+      <c r="I8" s="2">
+        <v>1000724673337</v>
+      </c>
+      <c r="J8" s="2">
         <v>1000531405424</v>
       </c>
       <c r="K8" s="1">
         <v>46116</v>
       </c>
-      <c r="L8">
+      <c r="L8" s="2">
         <v>251947763811</v>
       </c>
       <c r="M8" t="s">
@@ -1246,16 +1249,16 @@
       <c r="H9">
         <v>15000</v>
       </c>
-      <c r="I9">
-        <v>1000724673337</v>
-      </c>
-      <c r="J9">
+      <c r="I9" s="2">
+        <v>1000724673337</v>
+      </c>
+      <c r="J9" s="2">
         <v>1000553520502</v>
       </c>
       <c r="K9" s="1">
         <v>46140</v>
       </c>
-      <c r="L9">
+      <c r="L9" s="2">
         <v>251954846351</v>
       </c>
       <c r="M9" t="s">
@@ -1287,20 +1290,20 @@
       <c r="H10">
         <v>15000</v>
       </c>
-      <c r="I10">
-        <v>1000724673337</v>
-      </c>
-      <c r="J10">
+      <c r="I10" s="2">
+        <v>1000724673337</v>
+      </c>
+      <c r="J10" s="2">
         <v>1000289318236</v>
       </c>
       <c r="K10" s="1">
-        <v>46140</v>
-      </c>
-      <c r="L10">
+        <v>46133</v>
+      </c>
+      <c r="L10" s="2">
         <v>251926757080</v>
       </c>
       <c r="M10" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.3">
@@ -1328,16 +1331,16 @@
       <c r="H11">
         <v>15000</v>
       </c>
-      <c r="I11">
-        <v>1000724673337</v>
-      </c>
-      <c r="J11">
+      <c r="I11" s="2">
+        <v>1000724673337</v>
+      </c>
+      <c r="J11" s="2">
         <v>1000263206022</v>
       </c>
       <c r="K11" s="1">
         <v>46141</v>
       </c>
-      <c r="L11">
+      <c r="L11" s="2">
         <v>251935869198</v>
       </c>
       <c r="M11" t="s">
@@ -1369,16 +1372,16 @@
       <c r="H12">
         <v>15000</v>
       </c>
-      <c r="I12">
-        <v>1000724673337</v>
-      </c>
-      <c r="J12">
+      <c r="I12" s="2">
+        <v>1000724673337</v>
+      </c>
+      <c r="J12" s="2">
         <v>1000094217214</v>
       </c>
       <c r="K12" s="1">
         <v>46141</v>
       </c>
-      <c r="L12">
+      <c r="L12" s="2">
         <v>251923151481</v>
       </c>
       <c r="M12" t="s">
@@ -1410,16 +1413,16 @@
       <c r="H13">
         <v>15000</v>
       </c>
-      <c r="I13">
+      <c r="I13" s="2">
         <v>1000727672676</v>
       </c>
-      <c r="J13">
+      <c r="J13" s="2">
         <v>1000657475649</v>
       </c>
       <c r="K13" s="1">
         <v>46150</v>
       </c>
-      <c r="L13">
+      <c r="L13" s="2">
         <v>251919159451</v>
       </c>
       <c r="M13" t="s">
@@ -1451,16 +1454,16 @@
       <c r="H14">
         <v>15000</v>
       </c>
-      <c r="I14">
-        <v>1000724673337</v>
-      </c>
-      <c r="J14">
+      <c r="I14" s="2">
+        <v>1000724673337</v>
+      </c>
+      <c r="J14" s="2">
         <v>1000016351087</v>
       </c>
       <c r="K14" s="1">
         <v>46165</v>
       </c>
-      <c r="L14">
+      <c r="L14" s="2">
         <v>251912356447</v>
       </c>
       <c r="M14" t="s">
@@ -1492,16 +1495,16 @@
       <c r="H15">
         <v>15000</v>
       </c>
-      <c r="I15">
-        <v>1000724673337</v>
-      </c>
-      <c r="J15">
+      <c r="I15" s="2">
+        <v>1000724673337</v>
+      </c>
+      <c r="J15" s="2">
         <v>1000205376635</v>
       </c>
       <c r="K15" s="1">
         <v>46165</v>
       </c>
-      <c r="L15">
+      <c r="L15" s="2">
         <v>251922956646</v>
       </c>
       <c r="M15" t="s">
@@ -1533,16 +1536,16 @@
       <c r="H16">
         <v>15000</v>
       </c>
-      <c r="I16">
-        <v>1000724673337</v>
-      </c>
-      <c r="J16">
+      <c r="I16" s="2">
+        <v>1000724673337</v>
+      </c>
+      <c r="J16" s="2">
         <v>1000272980423</v>
       </c>
       <c r="K16" s="1">
         <v>46165</v>
       </c>
-      <c r="L16">
+      <c r="L16" s="2">
         <v>251911818685</v>
       </c>
       <c r="M16" t="s">
@@ -1574,16 +1577,16 @@
       <c r="H17">
         <v>15000</v>
       </c>
-      <c r="I17">
-        <v>1000724673337</v>
-      </c>
-      <c r="J17">
+      <c r="I17" s="2">
+        <v>1000724673337</v>
+      </c>
+      <c r="J17" s="2">
         <v>1000378957161</v>
       </c>
       <c r="K17" s="1">
         <v>46165</v>
       </c>
-      <c r="L17">
+      <c r="L17" s="2">
         <v>251930308503</v>
       </c>
       <c r="M17" t="s">
@@ -1615,16 +1618,16 @@
       <c r="H18">
         <v>100000</v>
       </c>
-      <c r="I18">
-        <v>1000724673337</v>
-      </c>
-      <c r="J18">
+      <c r="I18" s="2">
+        <v>1000724673337</v>
+      </c>
+      <c r="J18" s="2">
         <v>1000177190024</v>
       </c>
       <c r="K18" s="1">
         <v>46293</v>
       </c>
-      <c r="L18">
+      <c r="L18" s="2">
         <v>251912861288</v>
       </c>
       <c r="M18" t="s">
@@ -1633,7 +1636,7 @@
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A19">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="B19" s="1">
         <v>46115</v>
@@ -1656,16 +1659,16 @@
       <c r="H19">
         <v>100000</v>
       </c>
-      <c r="I19">
-        <v>1000724673337</v>
-      </c>
-      <c r="J19">
+      <c r="I19" s="2">
+        <v>1000724673337</v>
+      </c>
+      <c r="J19" s="2">
         <v>1000496218101</v>
       </c>
       <c r="K19" s="1">
         <v>46298</v>
       </c>
-      <c r="L19">
+      <c r="L19" s="2">
         <v>251977677737</v>
       </c>
       <c r="M19" t="s">
@@ -1674,7 +1677,7 @@
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A20">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="B20" s="1">
         <v>46116</v>
@@ -1697,16 +1700,16 @@
       <c r="H20">
         <v>25000</v>
       </c>
-      <c r="I20">
-        <v>1000724673337</v>
-      </c>
-      <c r="J20">
+      <c r="I20" s="2">
+        <v>1000724673337</v>
+      </c>
+      <c r="J20" s="2">
         <v>1000531405424</v>
       </c>
       <c r="K20" s="1">
         <v>46176</v>
       </c>
-      <c r="L20">
+      <c r="L20" s="2">
         <v>251947763811</v>
       </c>
       <c r="M20" t="s">
@@ -1715,7 +1718,7 @@
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A21">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="B21" s="1">
         <v>46123</v>
@@ -1738,23 +1741,65 @@
       <c r="H21">
         <v>100000</v>
       </c>
-      <c r="I21">
-        <v>1000724673337</v>
-      </c>
-      <c r="J21">
+      <c r="I21" s="2">
+        <v>1000724673337</v>
+      </c>
+      <c r="J21" s="2">
         <v>1000272980423</v>
       </c>
       <c r="K21" s="1">
         <v>46306</v>
       </c>
-      <c r="L21">
+      <c r="L21" s="2">
         <v>251911818685</v>
       </c>
       <c r="M21" t="s">
         <v>18</v>
       </c>
     </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22" s="1">
+        <v>46133</v>
+      </c>
+      <c r="C22">
+        <v>1010</v>
+      </c>
+      <c r="D22" t="s">
+        <v>17</v>
+      </c>
+      <c r="E22">
+        <v>21250</v>
+      </c>
+      <c r="F22">
+        <v>15</v>
+      </c>
+      <c r="G22">
+        <v>3750</v>
+      </c>
+      <c r="H22">
+        <v>25000</v>
+      </c>
+      <c r="I22" s="2">
+        <v>1000724673337</v>
+      </c>
+      <c r="J22" s="2">
+        <v>1000031177433</v>
+      </c>
+      <c r="K22" s="1">
+        <v>46194</v>
+      </c>
+      <c r="L22" s="2">
+        <v>251926757080</v>
+      </c>
+      <c r="M22" t="s">
+        <v>18</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/EGSA2025_short_loan.xlsx
+++ b/EGSA2025_short_loan.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="20">
   <si>
     <t>loan_id</t>
   </si>
@@ -887,13 +887,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M22"/>
+  <dimension ref="A1:M23"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.44140625" bestFit="1" customWidth="1"/>
     <col min="9" max="10" width="14.109375" style="2" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="10.5546875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="15.6640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.109375" style="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.3">
@@ -1256,13 +1261,13 @@
         <v>1000553520502</v>
       </c>
       <c r="K9" s="1">
-        <v>46140</v>
+        <v>46134</v>
       </c>
       <c r="L9" s="2">
         <v>251954846351</v>
       </c>
       <c r="M9" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.3">
@@ -1795,6 +1800,47 @@
         <v>251926757080</v>
       </c>
       <c r="M22" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="B23" s="1">
+        <v>46135</v>
+      </c>
+      <c r="C23">
+        <v>1007</v>
+      </c>
+      <c r="D23" t="s">
+        <v>17</v>
+      </c>
+      <c r="E23">
+        <v>21250</v>
+      </c>
+      <c r="F23">
+        <v>15</v>
+      </c>
+      <c r="G23">
+        <v>3750</v>
+      </c>
+      <c r="H23">
+        <v>25000</v>
+      </c>
+      <c r="I23" s="2">
+        <v>1000724673337</v>
+      </c>
+      <c r="J23" s="2">
+        <v>1000553520502</v>
+      </c>
+      <c r="K23" s="1">
+        <v>46196</v>
+      </c>
+      <c r="L23" s="2">
+        <v>251954846351</v>
+      </c>
+      <c r="M23" t="s">
         <v>18</v>
       </c>
     </row>

--- a/EGSA2025_short_loan.xlsx
+++ b/EGSA2025_short_loan.xlsx
@@ -891,14 +891,10 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.6640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.44140625" bestFit="1" customWidth="1"/>
     <col min="9" max="10" width="14.109375" style="2" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="10.5546875" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="13.109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.3">
@@ -1384,13 +1380,13 @@
         <v>1000094217214</v>
       </c>
       <c r="K12" s="1">
-        <v>46141</v>
+        <v>46137</v>
       </c>
       <c r="L12" s="2">
         <v>251923151481</v>
       </c>
       <c r="M12" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.3">

--- a/EGSA2025_short_loan.xlsx
+++ b/EGSA2025_short_loan.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="20">
   <si>
     <t>loan_id</t>
   </si>
@@ -887,14 +887,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M23"/>
+  <dimension ref="A1:M24"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="16.6640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.109375" style="2" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="10.5546875" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="13.109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="9.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.3">
@@ -1339,13 +1339,13 @@
         <v>1000263206022</v>
       </c>
       <c r="K11" s="1">
-        <v>46141</v>
+        <v>46139</v>
       </c>
       <c r="L11" s="2">
         <v>251935869198</v>
       </c>
       <c r="M11" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.3">
@@ -1837,6 +1837,47 @@
         <v>251954846351</v>
       </c>
       <c r="M23" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="B24" s="1">
+        <v>46139</v>
+      </c>
+      <c r="C24">
+        <v>1005</v>
+      </c>
+      <c r="D24" t="s">
+        <v>17</v>
+      </c>
+      <c r="E24">
+        <v>21250</v>
+      </c>
+      <c r="F24">
+        <v>15</v>
+      </c>
+      <c r="G24">
+        <v>3750</v>
+      </c>
+      <c r="H24">
+        <v>25000</v>
+      </c>
+      <c r="I24" s="2">
+        <v>1000724673337</v>
+      </c>
+      <c r="J24" s="2">
+        <v>1000263206022</v>
+      </c>
+      <c r="K24" s="1">
+        <v>46200</v>
+      </c>
+      <c r="L24" s="2">
+        <v>251935869198</v>
+      </c>
+      <c r="M24" t="s">
         <v>18</v>
       </c>
     </row>

--- a/EGSA2025_short_loan.xlsx
+++ b/EGSA2025_short_loan.xlsx
@@ -891,10 +891,11 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="16.6640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.109375" style="2" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="10.5546875" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="13.109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.3">
@@ -1544,13 +1545,13 @@
         <v>1000272980423</v>
       </c>
       <c r="K16" s="1">
-        <v>46165</v>
+        <v>46142</v>
       </c>
       <c r="L16" s="2">
         <v>251911818685</v>
       </c>
       <c r="M16" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.3">

--- a/EGSA2025_short_loan.xlsx
+++ b/EGSA2025_short_loan.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="10044"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="17256" windowHeight="6660"/>
   </bookViews>
   <sheets>
     <sheet name="EGSA2025_short_loan" sheetId="1" r:id="rId1"/>
@@ -891,11 +891,9 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.109375" bestFit="1" customWidth="1"/>
     <col min="9" max="10" width="14.109375" style="2" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="10.5546875" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="13.109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="9.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.3">
@@ -1422,13 +1420,13 @@
         <v>1000657475649</v>
       </c>
       <c r="K13" s="1">
-        <v>46150</v>
+        <v>46148</v>
       </c>
       <c r="L13" s="2">
         <v>251919159451</v>
       </c>
       <c r="M13" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.3">

--- a/EGSA2025_short_loan.xlsx
+++ b/EGSA2025_short_loan.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="17256" windowHeight="6660"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="10044"/>
   </bookViews>
   <sheets>
     <sheet name="EGSA2025_short_loan" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="20">
   <si>
     <t>loan_id</t>
   </si>
@@ -887,10 +887,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M24"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.5546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.44140625" bestFit="1" customWidth="1"/>
     <col min="9" max="10" width="14.109375" style="2" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="10.5546875" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="13.109375" style="2" bestFit="1" customWidth="1"/>
@@ -1880,6 +1883,47 @@
         <v>18</v>
       </c>
     </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A25">
+        <v>32</v>
+      </c>
+      <c r="B25" s="1">
+        <v>46150</v>
+      </c>
+      <c r="C25">
+        <v>1010</v>
+      </c>
+      <c r="D25" t="s">
+        <v>16</v>
+      </c>
+      <c r="E25">
+        <v>4750</v>
+      </c>
+      <c r="F25">
+        <v>5</v>
+      </c>
+      <c r="G25">
+        <v>250</v>
+      </c>
+      <c r="H25">
+        <v>5000</v>
+      </c>
+      <c r="I25" s="2">
+        <v>1000724673337</v>
+      </c>
+      <c r="J25" s="2">
+        <v>1000289318236</v>
+      </c>
+      <c r="K25" s="1">
+        <v>46165</v>
+      </c>
+      <c r="L25" s="2">
+        <v>251926757080</v>
+      </c>
+      <c r="M25" t="s">
+        <v>18</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/EGSA2025_short_loan.xlsx
+++ b/EGSA2025_short_loan.xlsx
@@ -891,9 +891,6 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.5546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.44140625" bestFit="1" customWidth="1"/>
     <col min="9" max="10" width="14.109375" style="2" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="10.5546875" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="13.109375" style="2" bestFit="1" customWidth="1"/>
@@ -1885,7 +1882,7 @@
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A25">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="B25" s="1">
         <v>46150</v>

--- a/EGSA2025_short_loan.xlsx
+++ b/EGSA2025_short_loan.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="20">
   <si>
     <t>loan_id</t>
   </si>
@@ -887,7 +887,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M25"/>
+  <dimension ref="A1:M26"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="12.44140625" bestFit="1" customWidth="1"/>
@@ -1921,6 +1921,47 @@
         <v>18</v>
       </c>
     </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A26">
+        <v>25</v>
+      </c>
+      <c r="B26" s="1">
+        <v>46151</v>
+      </c>
+      <c r="C26">
+        <v>1002</v>
+      </c>
+      <c r="D26" t="s">
+        <v>16</v>
+      </c>
+      <c r="E26">
+        <v>4750</v>
+      </c>
+      <c r="F26">
+        <v>5</v>
+      </c>
+      <c r="G26">
+        <v>250</v>
+      </c>
+      <c r="H26">
+        <v>5000</v>
+      </c>
+      <c r="I26" s="2">
+        <v>1000724673337</v>
+      </c>
+      <c r="J26" s="2">
+        <v>1000177190024</v>
+      </c>
+      <c r="K26" s="1">
+        <v>46166</v>
+      </c>
+      <c r="L26" s="2">
+        <v>251912861288</v>
+      </c>
+      <c r="M26" t="s">
+        <v>18</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/EGSA2025_short_loan.xlsx
+++ b/EGSA2025_short_loan.xlsx
@@ -891,6 +891,9 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.109375" bestFit="1" customWidth="1"/>
     <col min="9" max="10" width="14.109375" style="2" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="10.5546875" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="13.109375" style="2" bestFit="1" customWidth="1"/>
@@ -1461,13 +1464,13 @@
         <v>1000016351087</v>
       </c>
       <c r="K14" s="1">
-        <v>46165</v>
+        <v>46162</v>
       </c>
       <c r="L14" s="2">
         <v>251912356447</v>
       </c>
       <c r="M14" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.3">

--- a/EGSA2025_short_loan.xlsx
+++ b/EGSA2025_short_loan.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="20">
   <si>
     <t>loan_id</t>
   </si>
@@ -887,16 +887,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M26"/>
+  <dimension ref="A1:M28"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="12.44140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.21875" customWidth="1"/>
     <col min="5" max="5" width="16.109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.109375" style="2" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="10.5546875" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="13.109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.3">
@@ -1965,6 +1967,88 @@
         <v>18</v>
       </c>
     </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A27">
+        <v>26</v>
+      </c>
+      <c r="B27" s="1">
+        <v>46163</v>
+      </c>
+      <c r="C27">
+        <v>1001</v>
+      </c>
+      <c r="D27" t="s">
+        <v>17</v>
+      </c>
+      <c r="E27">
+        <v>21250</v>
+      </c>
+      <c r="F27">
+        <v>15</v>
+      </c>
+      <c r="G27">
+        <v>3750</v>
+      </c>
+      <c r="H27">
+        <v>25000</v>
+      </c>
+      <c r="I27" s="2">
+        <v>1000724673337</v>
+      </c>
+      <c r="J27" s="2">
+        <v>10001490488816</v>
+      </c>
+      <c r="K27" s="1">
+        <v>46224</v>
+      </c>
+      <c r="L27" s="2">
+        <v>251912672957</v>
+      </c>
+      <c r="M27" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A28">
+        <v>27</v>
+      </c>
+      <c r="B28" s="1">
+        <v>46163</v>
+      </c>
+      <c r="C28">
+        <v>1017</v>
+      </c>
+      <c r="D28" t="s">
+        <v>17</v>
+      </c>
+      <c r="E28">
+        <v>21250</v>
+      </c>
+      <c r="F28">
+        <v>15</v>
+      </c>
+      <c r="G28">
+        <v>3750</v>
+      </c>
+      <c r="H28">
+        <v>25000</v>
+      </c>
+      <c r="I28" s="2">
+        <v>1000724673337</v>
+      </c>
+      <c r="J28" s="2">
+        <v>1000016351087</v>
+      </c>
+      <c r="K28" s="1">
+        <v>46224</v>
+      </c>
+      <c r="L28" s="2">
+        <v>251912356447</v>
+      </c>
+      <c r="M28" t="s">
+        <v>18</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/EGSA2025_short_loan.xlsx
+++ b/EGSA2025_short_loan.xlsx
@@ -891,14 +891,11 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.21875" customWidth="1"/>
-    <col min="5" max="5" width="16.109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.6640625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="14.109375" style="2" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="15.109375" style="2" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="10.5546875" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="13.109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="9.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.3">
@@ -1589,13 +1586,13 @@
         <v>1000378957161</v>
       </c>
       <c r="K17" s="1">
-        <v>46165</v>
+        <v>46163</v>
       </c>
       <c r="L17" s="2">
         <v>251930308503</v>
       </c>
       <c r="M17" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.3">

--- a/EGSA2025_short_loan.xlsx
+++ b/EGSA2025_short_loan.xlsx
@@ -891,7 +891,6 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.6640625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="14.109375" style="2" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="15.109375" style="2" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="10.5546875" bestFit="1" customWidth="1"/>
@@ -1791,13 +1790,13 @@
         <v>1000031177433</v>
       </c>
       <c r="K22" s="1">
-        <v>46194</v>
+        <v>46164</v>
       </c>
       <c r="L22" s="2">
         <v>251926757080</v>
       </c>
       <c r="M22" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.3">
@@ -1914,13 +1913,13 @@
         <v>1000289318236</v>
       </c>
       <c r="K25" s="1">
-        <v>46165</v>
+        <v>46164</v>
       </c>
       <c r="L25" s="2">
         <v>251926757080</v>
       </c>
       <c r="M25" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.3">

--- a/EGSA2025_short_loan.xlsx
+++ b/EGSA2025_short_loan.xlsx
@@ -1954,13 +1954,13 @@
         <v>1000177190024</v>
       </c>
       <c r="K26" s="1">
-        <v>46166</v>
+        <v>46164</v>
       </c>
       <c r="L26" s="2">
         <v>251912861288</v>
       </c>
       <c r="M26" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.3">

--- a/EGSA2025_short_loan.xlsx
+++ b/EGSA2025_short_loan.xlsx
@@ -75,10 +75,10 @@
     <t>level_4</t>
   </si>
   <si>
-    <t>in progress</t>
+    <t>level_6</t>
   </si>
   <si>
-    <t>level_6</t>
+    <t>in progress</t>
   </si>
 </sst>
 </file>
@@ -1503,13 +1503,13 @@
         <v>1000205376635</v>
       </c>
       <c r="K15" s="1">
-        <v>46165</v>
+        <v>46164</v>
       </c>
       <c r="L15" s="2">
         <v>251922956646</v>
       </c>
       <c r="M15" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.3">
@@ -1605,7 +1605,7 @@
         <v>1002</v>
       </c>
       <c r="D18" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E18">
         <v>85000</v>
@@ -1632,7 +1632,7 @@
         <v>251912861288</v>
       </c>
       <c r="M18" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.3">
@@ -1646,7 +1646,7 @@
         <v>1003</v>
       </c>
       <c r="D19" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E19">
         <v>85000</v>
@@ -1673,7 +1673,7 @@
         <v>251977677737</v>
       </c>
       <c r="M19" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.3">
@@ -1714,7 +1714,7 @@
         <v>251947763811</v>
       </c>
       <c r="M20" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.3">
@@ -1728,7 +1728,7 @@
         <v>1006</v>
       </c>
       <c r="D21" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E21">
         <v>85000</v>
@@ -1755,7 +1755,7 @@
         <v>251911818685</v>
       </c>
       <c r="M21" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.3">
@@ -1837,7 +1837,7 @@
         <v>251954846351</v>
       </c>
       <c r="M23" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.3">
@@ -1878,7 +1878,7 @@
         <v>251935869198</v>
       </c>
       <c r="M24" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.3">
@@ -2001,7 +2001,7 @@
         <v>251912672957</v>
       </c>
       <c r="M27" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.3">
@@ -2042,7 +2042,7 @@
         <v>251912356447</v>
       </c>
       <c r="M28" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>

--- a/EGSA2025_short_loan.xlsx
+++ b/EGSA2025_short_loan.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="20">
   <si>
     <t>loan_id</t>
   </si>
@@ -887,7 +887,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M28"/>
+  <dimension ref="A1:M29"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="12.44140625" bestFit="1" customWidth="1"/>
@@ -2045,6 +2045,47 @@
         <v>19</v>
       </c>
     </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A29">
+        <v>28</v>
+      </c>
+      <c r="B29" s="1">
+        <v>46167</v>
+      </c>
+      <c r="C29">
+        <v>1002</v>
+      </c>
+      <c r="D29" t="s">
+        <v>13</v>
+      </c>
+      <c r="E29">
+        <v>13500</v>
+      </c>
+      <c r="F29">
+        <v>10</v>
+      </c>
+      <c r="G29">
+        <v>1500</v>
+      </c>
+      <c r="H29">
+        <v>15000</v>
+      </c>
+      <c r="I29" s="2">
+        <v>1000724673337</v>
+      </c>
+      <c r="J29" s="2">
+        <v>1000177190024</v>
+      </c>
+      <c r="K29" s="1">
+        <v>46198</v>
+      </c>
+      <c r="L29" s="2">
+        <v>251912861288</v>
+      </c>
+      <c r="M29" t="s">
+        <v>19</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/EGSA2025_short_loan.xlsx
+++ b/EGSA2025_short_loan.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="20">
   <si>
     <t>loan_id</t>
   </si>
@@ -887,7 +887,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M29"/>
+  <dimension ref="A1:M30"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="12.44140625" bestFit="1" customWidth="1"/>
@@ -2086,6 +2086,47 @@
         <v>19</v>
       </c>
     </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A30">
+        <v>29</v>
+      </c>
+      <c r="B30" s="1">
+        <v>46168</v>
+      </c>
+      <c r="C30">
+        <v>1008</v>
+      </c>
+      <c r="D30" t="s">
+        <v>18</v>
+      </c>
+      <c r="E30">
+        <v>85000</v>
+      </c>
+      <c r="F30">
+        <v>15</v>
+      </c>
+      <c r="G30">
+        <v>15000</v>
+      </c>
+      <c r="H30">
+        <v>100000</v>
+      </c>
+      <c r="I30" s="2">
+        <v>1000724673337</v>
+      </c>
+      <c r="J30" s="2">
+        <v>1000205376635</v>
+      </c>
+      <c r="K30" s="1">
+        <v>46352</v>
+      </c>
+      <c r="L30" s="2">
+        <v>251922956646</v>
+      </c>
+      <c r="M30" t="s">
+        <v>19</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/EGSA2025_short_loan.xlsx
+++ b/EGSA2025_short_loan.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="20">
   <si>
     <t>loan_id</t>
   </si>
@@ -887,7 +887,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M30"/>
+  <dimension ref="A1:M31"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="12.44140625" bestFit="1" customWidth="1"/>
@@ -1708,13 +1708,13 @@
         <v>1000531405424</v>
       </c>
       <c r="K20" s="1">
-        <v>46176</v>
+        <v>46175</v>
       </c>
       <c r="L20" s="2">
         <v>251947763811</v>
       </c>
       <c r="M20" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.3">
@@ -2124,6 +2124,47 @@
         <v>251922956646</v>
       </c>
       <c r="M30" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A31">
+        <v>30</v>
+      </c>
+      <c r="B31" s="1">
+        <v>46176</v>
+      </c>
+      <c r="C31">
+        <v>1011</v>
+      </c>
+      <c r="D31" t="s">
+        <v>17</v>
+      </c>
+      <c r="E31">
+        <v>21250</v>
+      </c>
+      <c r="F31">
+        <v>15</v>
+      </c>
+      <c r="G31">
+        <v>3750</v>
+      </c>
+      <c r="H31">
+        <v>25000</v>
+      </c>
+      <c r="I31" s="2">
+        <v>1000724673337</v>
+      </c>
+      <c r="J31" s="2">
+        <v>1000531405424</v>
+      </c>
+      <c r="K31" s="1">
+        <v>46237</v>
+      </c>
+      <c r="L31" s="2">
+        <v>251947763811</v>
+      </c>
+      <c r="M31" t="s">
         <v>19</v>
       </c>
     </row>

--- a/EGSA2025_short_loan.xlsx
+++ b/EGSA2025_short_loan.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="20">
   <si>
     <t>loan_id</t>
   </si>
@@ -887,7 +887,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M31"/>
+  <dimension ref="A1:M32"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="12.44140625" bestFit="1" customWidth="1"/>
@@ -2168,6 +2168,47 @@
         <v>19</v>
       </c>
     </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A32">
+        <v>31</v>
+      </c>
+      <c r="B32" s="1">
+        <v>46175</v>
+      </c>
+      <c r="C32">
+        <v>1010</v>
+      </c>
+      <c r="D32" t="s">
+        <v>15</v>
+      </c>
+      <c r="E32">
+        <v>9500</v>
+      </c>
+      <c r="F32">
+        <v>5</v>
+      </c>
+      <c r="G32">
+        <v>500</v>
+      </c>
+      <c r="H32">
+        <v>10000</v>
+      </c>
+      <c r="I32" s="2">
+        <v>1000724673337</v>
+      </c>
+      <c r="J32" s="2">
+        <v>1000289318236</v>
+      </c>
+      <c r="K32" s="1">
+        <v>46195</v>
+      </c>
+      <c r="L32" s="2">
+        <v>251926757080</v>
+      </c>
+      <c r="M32" t="s">
+        <v>19</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/EGSA2025_short_loan.xlsx
+++ b/EGSA2025_short_loan.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="20">
   <si>
     <t>loan_id</t>
   </si>
@@ -887,7 +887,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M32"/>
+  <dimension ref="A1:M33"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="12.44140625" bestFit="1" customWidth="1"/>
@@ -2209,6 +2209,47 @@
         <v>19</v>
       </c>
     </row>
+    <row r="33" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A33">
+        <v>32</v>
+      </c>
+      <c r="B33" s="1">
+        <v>46183</v>
+      </c>
+      <c r="C33">
+        <v>1010</v>
+      </c>
+      <c r="D33" t="s">
+        <v>18</v>
+      </c>
+      <c r="E33">
+        <v>85000</v>
+      </c>
+      <c r="F33">
+        <v>15</v>
+      </c>
+      <c r="G33">
+        <v>15000</v>
+      </c>
+      <c r="H33">
+        <v>100000</v>
+      </c>
+      <c r="I33" s="2">
+        <v>1000724673337</v>
+      </c>
+      <c r="J33" s="2">
+        <v>1000289318236</v>
+      </c>
+      <c r="K33" s="1">
+        <v>46366</v>
+      </c>
+      <c r="L33" s="2">
+        <v>251926757080</v>
+      </c>
+      <c r="M33" t="s">
+        <v>19</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/EGSA2025_short_loan.xlsx
+++ b/EGSA2025_short_loan.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="10044"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20724" windowHeight="3192"/>
   </bookViews>
   <sheets>
     <sheet name="EGSA2025_short_loan" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="20">
   <si>
     <t>loan_id</t>
   </si>
@@ -887,10 +887,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M33"/>
+  <dimension ref="A1:M34"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.109375" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="14.109375" style="2" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="15.109375" style="2" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="10.5546875" bestFit="1" customWidth="1"/>
@@ -1831,13 +1833,13 @@
         <v>1000553520502</v>
       </c>
       <c r="K23" s="1">
-        <v>46196</v>
+        <v>46195</v>
       </c>
       <c r="L23" s="2">
         <v>251954846351</v>
       </c>
       <c r="M23" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.3">
@@ -2200,7 +2202,7 @@
         <v>1000289318236</v>
       </c>
       <c r="K32" s="1">
-        <v>46195</v>
+        <v>46194</v>
       </c>
       <c r="L32" s="2">
         <v>251926757080</v>
@@ -2247,6 +2249,47 @@
         <v>251926757080</v>
       </c>
       <c r="M33" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A34">
+        <v>33</v>
+      </c>
+      <c r="B34" s="1">
+        <v>46196</v>
+      </c>
+      <c r="C34">
+        <v>1007</v>
+      </c>
+      <c r="D34" t="s">
+        <v>17</v>
+      </c>
+      <c r="E34">
+        <v>21250</v>
+      </c>
+      <c r="F34">
+        <v>15</v>
+      </c>
+      <c r="G34">
+        <v>3750</v>
+      </c>
+      <c r="H34">
+        <v>25000</v>
+      </c>
+      <c r="I34" s="2">
+        <v>1000724673337</v>
+      </c>
+      <c r="J34" s="2">
+        <v>1000553520502</v>
+      </c>
+      <c r="K34" s="1">
+        <v>46257</v>
+      </c>
+      <c r="L34" s="2">
+        <v>251954846351</v>
+      </c>
+      <c r="M34" t="s">
         <v>19</v>
       </c>
     </row>

--- a/EGSA2025_short_loan.xlsx
+++ b/EGSA2025_short_loan.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20724" windowHeight="3192"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="10044"/>
   </bookViews>
   <sheets>
     <sheet name="EGSA2025_short_loan" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="20">
   <si>
     <t>loan_id</t>
   </si>
@@ -887,15 +887,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M34"/>
+  <dimension ref="A1:M36"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.109375" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="14.109375" style="2" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="15.109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.5546875" style="1" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="13.109375" style="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -930,7 +928,7 @@
       <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
       <c r="L1" s="2" t="s">
@@ -2079,13 +2077,13 @@
         <v>1000177190024</v>
       </c>
       <c r="K29" s="1">
-        <v>46198</v>
+        <v>46166</v>
       </c>
       <c r="L29" s="2">
         <v>251912861288</v>
       </c>
       <c r="M29" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.3">
@@ -2208,7 +2206,7 @@
         <v>251926757080</v>
       </c>
       <c r="M32" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.3">
@@ -2290,6 +2288,88 @@
         <v>251954846351</v>
       </c>
       <c r="M34" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A35">
+        <v>34</v>
+      </c>
+      <c r="B35" s="1">
+        <v>46199</v>
+      </c>
+      <c r="C35">
+        <v>1002</v>
+      </c>
+      <c r="D35" t="s">
+        <v>13</v>
+      </c>
+      <c r="E35">
+        <v>13500</v>
+      </c>
+      <c r="F35">
+        <v>10</v>
+      </c>
+      <c r="G35">
+        <v>1500</v>
+      </c>
+      <c r="H35">
+        <v>15000</v>
+      </c>
+      <c r="I35" s="2">
+        <v>1000724673337</v>
+      </c>
+      <c r="J35" s="2">
+        <v>1000177190024</v>
+      </c>
+      <c r="K35" s="1">
+        <v>46229</v>
+      </c>
+      <c r="L35" s="2">
+        <v>251912861288</v>
+      </c>
+      <c r="M35" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A36">
+        <v>35</v>
+      </c>
+      <c r="B36" s="1">
+        <v>46199</v>
+      </c>
+      <c r="C36">
+        <v>1010</v>
+      </c>
+      <c r="D36" t="s">
+        <v>13</v>
+      </c>
+      <c r="E36">
+        <v>13500</v>
+      </c>
+      <c r="F36">
+        <v>10</v>
+      </c>
+      <c r="G36">
+        <v>1500</v>
+      </c>
+      <c r="H36">
+        <v>15000</v>
+      </c>
+      <c r="I36" s="2">
+        <v>1000724673337</v>
+      </c>
+      <c r="J36" s="2">
+        <v>1000289318236</v>
+      </c>
+      <c r="K36" s="1">
+        <v>46229</v>
+      </c>
+      <c r="L36" s="2">
+        <v>251926757080</v>
+      </c>
+      <c r="M36" t="s">
         <v>19</v>
       </c>
     </row>

--- a/EGSA2025_short_loan.xlsx
+++ b/EGSA2025_short_loan.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="20">
   <si>
     <t>loan_id</t>
   </si>
@@ -887,13 +887,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M36"/>
+  <dimension ref="A1:M37"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="12.44140625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="14.109375" style="2" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="15.109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.5546875" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="13.109375" style="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -928,7 +928,7 @@
       <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" t="s">
         <v>10</v>
       </c>
       <c r="L1" s="2" t="s">
@@ -1872,13 +1872,13 @@
         <v>1000263206022</v>
       </c>
       <c r="K24" s="1">
-        <v>46200</v>
+        <v>46199</v>
       </c>
       <c r="L24" s="2">
         <v>251935869198</v>
       </c>
       <c r="M24" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.3">
@@ -2370,6 +2370,47 @@
         <v>251926757080</v>
       </c>
       <c r="M36" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A37">
+        <v>36</v>
+      </c>
+      <c r="B37" s="1">
+        <v>46200</v>
+      </c>
+      <c r="C37">
+        <v>1005</v>
+      </c>
+      <c r="D37" t="s">
+        <v>17</v>
+      </c>
+      <c r="E37">
+        <v>21250</v>
+      </c>
+      <c r="F37">
+        <v>15</v>
+      </c>
+      <c r="G37">
+        <v>3750</v>
+      </c>
+      <c r="H37">
+        <v>25000</v>
+      </c>
+      <c r="I37" s="2">
+        <v>1000724673337</v>
+      </c>
+      <c r="J37" s="2">
+        <v>1000263206022</v>
+      </c>
+      <c r="K37" s="1">
+        <v>46261</v>
+      </c>
+      <c r="L37" s="2">
+        <v>251935869198</v>
+      </c>
+      <c r="M37" t="s">
         <v>19</v>
       </c>
     </row>

--- a/EGSA2025_short_loan.xlsx
+++ b/EGSA2025_short_loan.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="20">
   <si>
     <t>loan_id</t>
   </si>
@@ -887,11 +887,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M37"/>
+  <dimension ref="A1:M39"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.109375" style="2" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="15.109375" style="2" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="10.5546875" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="13.109375" style="2" bestFit="1" customWidth="1"/>
@@ -922,7 +921,7 @@
       <c r="H1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" t="s">
         <v>8</v>
       </c>
       <c r="J1" s="2" t="s">
@@ -963,7 +962,7 @@
       <c r="H2">
         <v>10000</v>
       </c>
-      <c r="I2" s="2">
+      <c r="I2">
         <v>1000724673337</v>
       </c>
       <c r="J2" s="2">
@@ -1004,7 +1003,7 @@
       <c r="H3">
         <v>5000</v>
       </c>
-      <c r="I3" s="2">
+      <c r="I3">
         <v>1000724673337</v>
       </c>
       <c r="J3" s="2">
@@ -1045,7 +1044,7 @@
       <c r="H4">
         <v>2000</v>
       </c>
-      <c r="I4" s="2">
+      <c r="I4">
         <v>1000724673337</v>
       </c>
       <c r="J4" s="2">
@@ -1086,7 +1085,7 @@
       <c r="H5">
         <v>15000</v>
       </c>
-      <c r="I5" s="2">
+      <c r="I5">
         <v>1000724673337</v>
       </c>
       <c r="J5" s="2">
@@ -1127,7 +1126,7 @@
       <c r="H6">
         <v>5000</v>
       </c>
-      <c r="I6" s="2">
+      <c r="I6">
         <v>1000724673337</v>
       </c>
       <c r="J6" s="2">
@@ -1168,7 +1167,7 @@
       <c r="H7">
         <v>15000</v>
       </c>
-      <c r="I7" s="2">
+      <c r="I7">
         <v>1000724673337</v>
       </c>
       <c r="J7" s="2">
@@ -1209,7 +1208,7 @@
       <c r="H8">
         <v>15000</v>
       </c>
-      <c r="I8" s="2">
+      <c r="I8">
         <v>1000724673337</v>
       </c>
       <c r="J8" s="2">
@@ -1250,7 +1249,7 @@
       <c r="H9">
         <v>15000</v>
       </c>
-      <c r="I9" s="2">
+      <c r="I9">
         <v>1000724673337</v>
       </c>
       <c r="J9" s="2">
@@ -1291,7 +1290,7 @@
       <c r="H10">
         <v>15000</v>
       </c>
-      <c r="I10" s="2">
+      <c r="I10">
         <v>1000724673337</v>
       </c>
       <c r="J10" s="2">
@@ -1332,7 +1331,7 @@
       <c r="H11">
         <v>15000</v>
       </c>
-      <c r="I11" s="2">
+      <c r="I11">
         <v>1000724673337</v>
       </c>
       <c r="J11" s="2">
@@ -1373,7 +1372,7 @@
       <c r="H12">
         <v>15000</v>
       </c>
-      <c r="I12" s="2">
+      <c r="I12">
         <v>1000724673337</v>
       </c>
       <c r="J12" s="2">
@@ -1414,7 +1413,7 @@
       <c r="H13">
         <v>15000</v>
       </c>
-      <c r="I13" s="2">
+      <c r="I13">
         <v>1000727672676</v>
       </c>
       <c r="J13" s="2">
@@ -1455,7 +1454,7 @@
       <c r="H14">
         <v>15000</v>
       </c>
-      <c r="I14" s="2">
+      <c r="I14">
         <v>1000724673337</v>
       </c>
       <c r="J14" s="2">
@@ -1496,7 +1495,7 @@
       <c r="H15">
         <v>15000</v>
       </c>
-      <c r="I15" s="2">
+      <c r="I15">
         <v>1000724673337</v>
       </c>
       <c r="J15" s="2">
@@ -1537,7 +1536,7 @@
       <c r="H16">
         <v>15000</v>
       </c>
-      <c r="I16" s="2">
+      <c r="I16">
         <v>1000724673337</v>
       </c>
       <c r="J16" s="2">
@@ -1578,7 +1577,7 @@
       <c r="H17">
         <v>15000</v>
       </c>
-      <c r="I17" s="2">
+      <c r="I17">
         <v>1000724673337</v>
       </c>
       <c r="J17" s="2">
@@ -1619,7 +1618,7 @@
       <c r="H18">
         <v>100000</v>
       </c>
-      <c r="I18" s="2">
+      <c r="I18">
         <v>1000724673337</v>
       </c>
       <c r="J18" s="2">
@@ -1660,7 +1659,7 @@
       <c r="H19">
         <v>100000</v>
       </c>
-      <c r="I19" s="2">
+      <c r="I19">
         <v>1000724673337</v>
       </c>
       <c r="J19" s="2">
@@ -1701,7 +1700,7 @@
       <c r="H20">
         <v>25000</v>
       </c>
-      <c r="I20" s="2">
+      <c r="I20">
         <v>1000724673337</v>
       </c>
       <c r="J20" s="2">
@@ -1742,7 +1741,7 @@
       <c r="H21">
         <v>100000</v>
       </c>
-      <c r="I21" s="2">
+      <c r="I21">
         <v>1000724673337</v>
       </c>
       <c r="J21" s="2">
@@ -1783,7 +1782,7 @@
       <c r="H22">
         <v>25000</v>
       </c>
-      <c r="I22" s="2">
+      <c r="I22">
         <v>1000724673337</v>
       </c>
       <c r="J22" s="2">
@@ -1824,7 +1823,7 @@
       <c r="H23">
         <v>25000</v>
       </c>
-      <c r="I23" s="2">
+      <c r="I23">
         <v>1000724673337</v>
       </c>
       <c r="J23" s="2">
@@ -1865,7 +1864,7 @@
       <c r="H24">
         <v>25000</v>
       </c>
-      <c r="I24" s="2">
+      <c r="I24">
         <v>1000724673337</v>
       </c>
       <c r="J24" s="2">
@@ -1906,7 +1905,7 @@
       <c r="H25">
         <v>5000</v>
       </c>
-      <c r="I25" s="2">
+      <c r="I25">
         <v>1000724673337</v>
       </c>
       <c r="J25" s="2">
@@ -1947,7 +1946,7 @@
       <c r="H26">
         <v>5000</v>
       </c>
-      <c r="I26" s="2">
+      <c r="I26">
         <v>1000724673337</v>
       </c>
       <c r="J26" s="2">
@@ -1988,7 +1987,7 @@
       <c r="H27">
         <v>25000</v>
       </c>
-      <c r="I27" s="2">
+      <c r="I27">
         <v>1000724673337</v>
       </c>
       <c r="J27" s="2">
@@ -2029,7 +2028,7 @@
       <c r="H28">
         <v>25000</v>
       </c>
-      <c r="I28" s="2">
+      <c r="I28">
         <v>1000724673337</v>
       </c>
       <c r="J28" s="2">
@@ -2070,7 +2069,7 @@
       <c r="H29">
         <v>15000</v>
       </c>
-      <c r="I29" s="2">
+      <c r="I29">
         <v>1000724673337</v>
       </c>
       <c r="J29" s="2">
@@ -2111,7 +2110,7 @@
       <c r="H30">
         <v>100000</v>
       </c>
-      <c r="I30" s="2">
+      <c r="I30">
         <v>1000724673337</v>
       </c>
       <c r="J30" s="2">
@@ -2152,7 +2151,7 @@
       <c r="H31">
         <v>25000</v>
       </c>
-      <c r="I31" s="2">
+      <c r="I31">
         <v>1000724673337</v>
       </c>
       <c r="J31" s="2">
@@ -2193,7 +2192,7 @@
       <c r="H32">
         <v>10000</v>
       </c>
-      <c r="I32" s="2">
+      <c r="I32">
         <v>1000724673337</v>
       </c>
       <c r="J32" s="2">
@@ -2234,7 +2233,7 @@
       <c r="H33">
         <v>100000</v>
       </c>
-      <c r="I33" s="2">
+      <c r="I33">
         <v>1000724673337</v>
       </c>
       <c r="J33" s="2">
@@ -2247,7 +2246,7 @@
         <v>251926757080</v>
       </c>
       <c r="M33" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.3">
@@ -2275,7 +2274,7 @@
       <c r="H34">
         <v>25000</v>
       </c>
-      <c r="I34" s="2">
+      <c r="I34">
         <v>1000724673337</v>
       </c>
       <c r="J34" s="2">
@@ -2316,7 +2315,7 @@
       <c r="H35">
         <v>15000</v>
       </c>
-      <c r="I35" s="2">
+      <c r="I35">
         <v>1000724673337</v>
       </c>
       <c r="J35" s="2">
@@ -2357,7 +2356,7 @@
       <c r="H36">
         <v>15000</v>
       </c>
-      <c r="I36" s="2">
+      <c r="I36">
         <v>1000724673337</v>
       </c>
       <c r="J36" s="2">
@@ -2398,7 +2397,7 @@
       <c r="H37">
         <v>25000</v>
       </c>
-      <c r="I37" s="2">
+      <c r="I37">
         <v>1000724673337</v>
       </c>
       <c r="J37" s="2">
@@ -2411,6 +2410,88 @@
         <v>251935869198</v>
       </c>
       <c r="M37" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A38">
+        <v>37</v>
+      </c>
+      <c r="B38" s="1">
+        <v>46203</v>
+      </c>
+      <c r="C38">
+        <v>1008</v>
+      </c>
+      <c r="D38" t="s">
+        <v>13</v>
+      </c>
+      <c r="E38">
+        <v>13500</v>
+      </c>
+      <c r="F38">
+        <v>10</v>
+      </c>
+      <c r="G38">
+        <v>1500</v>
+      </c>
+      <c r="H38">
+        <v>15000</v>
+      </c>
+      <c r="I38">
+        <v>1000724673337</v>
+      </c>
+      <c r="J38" s="2">
+        <v>1000205376635</v>
+      </c>
+      <c r="K38" s="1">
+        <v>46233</v>
+      </c>
+      <c r="L38" s="2">
+        <v>251922956646</v>
+      </c>
+      <c r="M38" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A39">
+        <v>38</v>
+      </c>
+      <c r="B39" s="1">
+        <v>46203</v>
+      </c>
+      <c r="C39">
+        <v>1003</v>
+      </c>
+      <c r="D39" t="s">
+        <v>13</v>
+      </c>
+      <c r="E39">
+        <v>13500</v>
+      </c>
+      <c r="F39">
+        <v>10</v>
+      </c>
+      <c r="G39">
+        <v>1500</v>
+      </c>
+      <c r="H39">
+        <v>15000</v>
+      </c>
+      <c r="I39">
+        <v>1000724673337</v>
+      </c>
+      <c r="J39" s="2">
+        <v>1000496218101</v>
+      </c>
+      <c r="K39" s="1">
+        <v>46233</v>
+      </c>
+      <c r="L39" s="2">
+        <v>251977677737</v>
+      </c>
+      <c r="M39" t="s">
         <v>19</v>
       </c>
     </row>

--- a/EGSA2025_short_loan.xlsx
+++ b/EGSA2025_short_loan.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="20">
   <si>
     <t>loan_id</t>
   </si>
@@ -887,10 +887,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M39"/>
+  <dimension ref="A1:M40"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.109375" style="2" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="15.109375" style="2" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="10.5546875" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="13.109375" style="2" bestFit="1" customWidth="1"/>
@@ -921,7 +922,7 @@
       <c r="H1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
       <c r="J1" s="2" t="s">
@@ -962,7 +963,7 @@
       <c r="H2">
         <v>10000</v>
       </c>
-      <c r="I2">
+      <c r="I2" s="2">
         <v>1000724673337</v>
       </c>
       <c r="J2" s="2">
@@ -1003,7 +1004,7 @@
       <c r="H3">
         <v>5000</v>
       </c>
-      <c r="I3">
+      <c r="I3" s="2">
         <v>1000724673337</v>
       </c>
       <c r="J3" s="2">
@@ -1044,7 +1045,7 @@
       <c r="H4">
         <v>2000</v>
       </c>
-      <c r="I4">
+      <c r="I4" s="2">
         <v>1000724673337</v>
       </c>
       <c r="J4" s="2">
@@ -1085,7 +1086,7 @@
       <c r="H5">
         <v>15000</v>
       </c>
-      <c r="I5">
+      <c r="I5" s="2">
         <v>1000724673337</v>
       </c>
       <c r="J5" s="2">
@@ -1126,7 +1127,7 @@
       <c r="H6">
         <v>5000</v>
       </c>
-      <c r="I6">
+      <c r="I6" s="2">
         <v>1000724673337</v>
       </c>
       <c r="J6" s="2">
@@ -1167,7 +1168,7 @@
       <c r="H7">
         <v>15000</v>
       </c>
-      <c r="I7">
+      <c r="I7" s="2">
         <v>1000724673337</v>
       </c>
       <c r="J7" s="2">
@@ -1208,7 +1209,7 @@
       <c r="H8">
         <v>15000</v>
       </c>
-      <c r="I8">
+      <c r="I8" s="2">
         <v>1000724673337</v>
       </c>
       <c r="J8" s="2">
@@ -1249,7 +1250,7 @@
       <c r="H9">
         <v>15000</v>
       </c>
-      <c r="I9">
+      <c r="I9" s="2">
         <v>1000724673337</v>
       </c>
       <c r="J9" s="2">
@@ -1290,7 +1291,7 @@
       <c r="H10">
         <v>15000</v>
       </c>
-      <c r="I10">
+      <c r="I10" s="2">
         <v>1000724673337</v>
       </c>
       <c r="J10" s="2">
@@ -1331,7 +1332,7 @@
       <c r="H11">
         <v>15000</v>
       </c>
-      <c r="I11">
+      <c r="I11" s="2">
         <v>1000724673337</v>
       </c>
       <c r="J11" s="2">
@@ -1372,7 +1373,7 @@
       <c r="H12">
         <v>15000</v>
       </c>
-      <c r="I12">
+      <c r="I12" s="2">
         <v>1000724673337</v>
       </c>
       <c r="J12" s="2">
@@ -1413,7 +1414,7 @@
       <c r="H13">
         <v>15000</v>
       </c>
-      <c r="I13">
+      <c r="I13" s="2">
         <v>1000727672676</v>
       </c>
       <c r="J13" s="2">
@@ -1454,7 +1455,7 @@
       <c r="H14">
         <v>15000</v>
       </c>
-      <c r="I14">
+      <c r="I14" s="2">
         <v>1000724673337</v>
       </c>
       <c r="J14" s="2">
@@ -1495,7 +1496,7 @@
       <c r="H15">
         <v>15000</v>
       </c>
-      <c r="I15">
+      <c r="I15" s="2">
         <v>1000724673337</v>
       </c>
       <c r="J15" s="2">
@@ -1536,7 +1537,7 @@
       <c r="H16">
         <v>15000</v>
       </c>
-      <c r="I16">
+      <c r="I16" s="2">
         <v>1000724673337</v>
       </c>
       <c r="J16" s="2">
@@ -1577,7 +1578,7 @@
       <c r="H17">
         <v>15000</v>
       </c>
-      <c r="I17">
+      <c r="I17" s="2">
         <v>1000724673337</v>
       </c>
       <c r="J17" s="2">
@@ -1618,7 +1619,7 @@
       <c r="H18">
         <v>100000</v>
       </c>
-      <c r="I18">
+      <c r="I18" s="2">
         <v>1000724673337</v>
       </c>
       <c r="J18" s="2">
@@ -1659,7 +1660,7 @@
       <c r="H19">
         <v>100000</v>
       </c>
-      <c r="I19">
+      <c r="I19" s="2">
         <v>1000724673337</v>
       </c>
       <c r="J19" s="2">
@@ -1700,7 +1701,7 @@
       <c r="H20">
         <v>25000</v>
       </c>
-      <c r="I20">
+      <c r="I20" s="2">
         <v>1000724673337</v>
       </c>
       <c r="J20" s="2">
@@ -1741,7 +1742,7 @@
       <c r="H21">
         <v>100000</v>
       </c>
-      <c r="I21">
+      <c r="I21" s="2">
         <v>1000724673337</v>
       </c>
       <c r="J21" s="2">
@@ -1782,7 +1783,7 @@
       <c r="H22">
         <v>25000</v>
       </c>
-      <c r="I22">
+      <c r="I22" s="2">
         <v>1000724673337</v>
       </c>
       <c r="J22" s="2">
@@ -1823,7 +1824,7 @@
       <c r="H23">
         <v>25000</v>
       </c>
-      <c r="I23">
+      <c r="I23" s="2">
         <v>1000724673337</v>
       </c>
       <c r="J23" s="2">
@@ -1864,7 +1865,7 @@
       <c r="H24">
         <v>25000</v>
       </c>
-      <c r="I24">
+      <c r="I24" s="2">
         <v>1000724673337</v>
       </c>
       <c r="J24" s="2">
@@ -1905,7 +1906,7 @@
       <c r="H25">
         <v>5000</v>
       </c>
-      <c r="I25">
+      <c r="I25" s="2">
         <v>1000724673337</v>
       </c>
       <c r="J25" s="2">
@@ -1946,7 +1947,7 @@
       <c r="H26">
         <v>5000</v>
       </c>
-      <c r="I26">
+      <c r="I26" s="2">
         <v>1000724673337</v>
       </c>
       <c r="J26" s="2">
@@ -1987,7 +1988,7 @@
       <c r="H27">
         <v>25000</v>
       </c>
-      <c r="I27">
+      <c r="I27" s="2">
         <v>1000724673337</v>
       </c>
       <c r="J27" s="2">
@@ -2028,7 +2029,7 @@
       <c r="H28">
         <v>25000</v>
       </c>
-      <c r="I28">
+      <c r="I28" s="2">
         <v>1000724673337</v>
       </c>
       <c r="J28" s="2">
@@ -2069,7 +2070,7 @@
       <c r="H29">
         <v>15000</v>
       </c>
-      <c r="I29">
+      <c r="I29" s="2">
         <v>1000724673337</v>
       </c>
       <c r="J29" s="2">
@@ -2110,7 +2111,7 @@
       <c r="H30">
         <v>100000</v>
       </c>
-      <c r="I30">
+      <c r="I30" s="2">
         <v>1000724673337</v>
       </c>
       <c r="J30" s="2">
@@ -2151,7 +2152,7 @@
       <c r="H31">
         <v>25000</v>
       </c>
-      <c r="I31">
+      <c r="I31" s="2">
         <v>1000724673337</v>
       </c>
       <c r="J31" s="2">
@@ -2192,7 +2193,7 @@
       <c r="H32">
         <v>10000</v>
       </c>
-      <c r="I32">
+      <c r="I32" s="2">
         <v>1000724673337</v>
       </c>
       <c r="J32" s="2">
@@ -2233,7 +2234,7 @@
       <c r="H33">
         <v>100000</v>
       </c>
-      <c r="I33">
+      <c r="I33" s="2">
         <v>1000724673337</v>
       </c>
       <c r="J33" s="2">
@@ -2274,7 +2275,7 @@
       <c r="H34">
         <v>25000</v>
       </c>
-      <c r="I34">
+      <c r="I34" s="2">
         <v>1000724673337</v>
       </c>
       <c r="J34" s="2">
@@ -2315,7 +2316,7 @@
       <c r="H35">
         <v>15000</v>
       </c>
-      <c r="I35">
+      <c r="I35" s="2">
         <v>1000724673337</v>
       </c>
       <c r="J35" s="2">
@@ -2356,7 +2357,7 @@
       <c r="H36">
         <v>15000</v>
       </c>
-      <c r="I36">
+      <c r="I36" s="2">
         <v>1000724673337</v>
       </c>
       <c r="J36" s="2">
@@ -2397,7 +2398,7 @@
       <c r="H37">
         <v>25000</v>
       </c>
-      <c r="I37">
+      <c r="I37" s="2">
         <v>1000724673337</v>
       </c>
       <c r="J37" s="2">
@@ -2438,7 +2439,7 @@
       <c r="H38">
         <v>15000</v>
       </c>
-      <c r="I38">
+      <c r="I38" s="2">
         <v>1000724673337</v>
       </c>
       <c r="J38" s="2">
@@ -2479,7 +2480,7 @@
       <c r="H39">
         <v>15000</v>
       </c>
-      <c r="I39">
+      <c r="I39" s="2">
         <v>1000724673337</v>
       </c>
       <c r="J39" s="2">
@@ -2492,6 +2493,47 @@
         <v>251977677737</v>
       </c>
       <c r="M39" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A40">
+        <v>39</v>
+      </c>
+      <c r="B40" s="1">
+        <v>46204</v>
+      </c>
+      <c r="C40">
+        <v>1020</v>
+      </c>
+      <c r="D40" t="s">
+        <v>17</v>
+      </c>
+      <c r="E40">
+        <v>21250</v>
+      </c>
+      <c r="F40">
+        <v>15</v>
+      </c>
+      <c r="G40">
+        <v>3750</v>
+      </c>
+      <c r="H40">
+        <v>25000</v>
+      </c>
+      <c r="I40" s="2">
+        <v>1000724673337</v>
+      </c>
+      <c r="J40" s="2">
+        <v>1000016981088</v>
+      </c>
+      <c r="K40" s="1">
+        <v>46266</v>
+      </c>
+      <c r="L40" s="2">
+        <v>251902666362</v>
+      </c>
+      <c r="M40" t="s">
         <v>19</v>
       </c>
     </row>

--- a/EGSA2025_short_loan.xlsx
+++ b/EGSA2025_short_loan.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="20">
   <si>
     <t>loan_id</t>
   </si>
@@ -887,7 +887,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M40"/>
+  <dimension ref="A1:M41"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="12.44140625" bestFit="1" customWidth="1"/>
@@ -2036,13 +2036,13 @@
         <v>1000016351087</v>
       </c>
       <c r="K28" s="1">
-        <v>46224</v>
+        <v>46205</v>
       </c>
       <c r="L28" s="2">
         <v>251912356447</v>
       </c>
       <c r="M28" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.3">
@@ -2534,6 +2534,47 @@
         <v>251902666362</v>
       </c>
       <c r="M40" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A41">
+        <v>40</v>
+      </c>
+      <c r="B41" s="1">
+        <v>46205</v>
+      </c>
+      <c r="C41">
+        <v>1017</v>
+      </c>
+      <c r="D41" t="s">
+        <v>17</v>
+      </c>
+      <c r="E41">
+        <v>21250</v>
+      </c>
+      <c r="F41">
+        <v>15</v>
+      </c>
+      <c r="G41">
+        <v>3750</v>
+      </c>
+      <c r="H41">
+        <v>25000</v>
+      </c>
+      <c r="I41" s="2">
+        <v>1000724673337</v>
+      </c>
+      <c r="J41" s="2">
+        <v>1000016351087</v>
+      </c>
+      <c r="K41" s="1">
+        <v>46267</v>
+      </c>
+      <c r="L41" s="2">
+        <v>251912356447</v>
+      </c>
+      <c r="M41" t="s">
         <v>19</v>
       </c>
     </row>

--- a/EGSA2025_short_loan.xlsx
+++ b/EGSA2025_short_loan.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="20">
   <si>
     <t>loan_id</t>
   </si>
@@ -887,7 +887,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M41"/>
+  <dimension ref="A1:M43"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="12.44140625" bestFit="1" customWidth="1"/>
@@ -2578,6 +2578,88 @@
         <v>19</v>
       </c>
     </row>
+    <row r="42" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A42">
+        <v>41</v>
+      </c>
+      <c r="B42" s="1">
+        <v>46206</v>
+      </c>
+      <c r="C42">
+        <v>1026</v>
+      </c>
+      <c r="D42" t="s">
+        <v>17</v>
+      </c>
+      <c r="E42">
+        <v>21250</v>
+      </c>
+      <c r="F42">
+        <v>15</v>
+      </c>
+      <c r="G42">
+        <v>3750</v>
+      </c>
+      <c r="H42">
+        <v>25000</v>
+      </c>
+      <c r="I42" s="2">
+        <v>1000724673337</v>
+      </c>
+      <c r="J42" s="2">
+        <v>1000548538797</v>
+      </c>
+      <c r="K42" s="1">
+        <v>46268</v>
+      </c>
+      <c r="L42" s="2">
+        <v>251965224695</v>
+      </c>
+      <c r="M42" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A43">
+        <v>42</v>
+      </c>
+      <c r="B43" s="1">
+        <v>46206</v>
+      </c>
+      <c r="C43">
+        <v>1023</v>
+      </c>
+      <c r="D43" t="s">
+        <v>16</v>
+      </c>
+      <c r="E43">
+        <v>4750</v>
+      </c>
+      <c r="F43">
+        <v>5</v>
+      </c>
+      <c r="G43">
+        <v>250</v>
+      </c>
+      <c r="H43">
+        <v>5000</v>
+      </c>
+      <c r="I43" s="2">
+        <v>1000724673337</v>
+      </c>
+      <c r="J43" s="2">
+        <v>1000657475649</v>
+      </c>
+      <c r="K43" s="1">
+        <v>46268</v>
+      </c>
+      <c r="L43" s="2">
+        <v>251919159451</v>
+      </c>
+      <c r="M43" t="s">
+        <v>19</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/EGSA2025_short_loan.xlsx
+++ b/EGSA2025_short_loan.xlsx
@@ -1421,7 +1421,7 @@
         <v>1000657475649</v>
       </c>
       <c r="K13" s="1">
-        <v>46148</v>
+        <v>46221</v>
       </c>
       <c r="L13" s="2">
         <v>251919159451</v>
@@ -2651,7 +2651,7 @@
         <v>1000657475649</v>
       </c>
       <c r="K43" s="1">
-        <v>46268</v>
+        <v>46221</v>
       </c>
       <c r="L43" s="2">
         <v>251919159451</v>

--- a/EGSA2025_short_loan.xlsx
+++ b/EGSA2025_short_loan.xlsx
@@ -1421,7 +1421,7 @@
         <v>1000657475649</v>
       </c>
       <c r="K13" s="1">
-        <v>46221</v>
+        <v>46149</v>
       </c>
       <c r="L13" s="2">
         <v>251919159451</v>

--- a/EGSA2025_short_loan.xlsx
+++ b/EGSA2025_short_loan.xlsx
@@ -895,6 +895,7 @@
     <col min="10" max="10" width="15.109375" style="2" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="10.5546875" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="13.109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.3">
@@ -2651,13 +2652,13 @@
         <v>1000657475649</v>
       </c>
       <c r="K43" s="1">
-        <v>46221</v>
+        <v>46220</v>
       </c>
       <c r="L43" s="2">
         <v>251919159451</v>
       </c>
       <c r="M43" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>

--- a/EGSA2025_short_loan.xlsx
+++ b/EGSA2025_short_loan.xlsx
@@ -895,7 +895,6 @@
     <col min="10" max="10" width="15.109375" style="2" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="10.5546875" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="13.109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="9.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.3">

--- a/EGSA2025_short_loan.xlsx
+++ b/EGSA2025_short_loan.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\walfaanaam\Desktop\general\EGSA_short_term\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Waltana\Desktop from C\general\EGSA_short_term\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -2364,13 +2364,13 @@
         <v>1000289318236</v>
       </c>
       <c r="K36" s="1">
-        <v>46229</v>
+        <v>46223</v>
       </c>
       <c r="L36" s="2">
         <v>251926757080</v>
       </c>
       <c r="M36" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
     </row>
     <row r="37" spans="1:13" x14ac:dyDescent="0.3">

--- a/EGSA2025_short_loan.xlsx
+++ b/EGSA2025_short_loan.xlsx
@@ -1995,13 +1995,13 @@
         <v>10001490488816</v>
       </c>
       <c r="K27" s="1">
-        <v>46224</v>
+        <v>46223</v>
       </c>
       <c r="L27" s="2">
         <v>251912672957</v>
       </c>
       <c r="M27" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.3">

--- a/EGSA2025_short_loan.xlsx
+++ b/EGSA2025_short_loan.xlsx
@@ -1011,7 +1011,7 @@
         <v>1000177190024</v>
       </c>
       <c r="K3" s="1">
-        <v>46077</v>
+        <v>46227</v>
       </c>
       <c r="L3" s="2">
         <v>251912861288</v>
@@ -1175,7 +1175,7 @@
         <v>1000177190024</v>
       </c>
       <c r="K7" s="1">
-        <v>46109</v>
+        <v>46227</v>
       </c>
       <c r="L7" s="2">
         <v>251912861288</v>
@@ -1626,7 +1626,7 @@
         <v>1000177190024</v>
       </c>
       <c r="K18" s="1">
-        <v>46293</v>
+        <v>46227</v>
       </c>
       <c r="L18" s="2">
         <v>251912861288</v>
@@ -1954,7 +1954,7 @@
         <v>1000177190024</v>
       </c>
       <c r="K26" s="1">
-        <v>46164</v>
+        <v>46227</v>
       </c>
       <c r="L26" s="2">
         <v>251912861288</v>
@@ -2077,7 +2077,7 @@
         <v>1000177190024</v>
       </c>
       <c r="K29" s="1">
-        <v>46166</v>
+        <v>46227</v>
       </c>
       <c r="L29" s="2">
         <v>251912861288</v>
@@ -2323,13 +2323,13 @@
         <v>1000177190024</v>
       </c>
       <c r="K35" s="1">
-        <v>46229</v>
+        <v>46227</v>
       </c>
       <c r="L35" s="2">
         <v>251912861288</v>
       </c>
       <c r="M35" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
     </row>
     <row r="36" spans="1:13" x14ac:dyDescent="0.3">

--- a/EGSA2025_short_loan.xlsx
+++ b/EGSA2025_short_loan.xlsx
@@ -894,7 +894,7 @@
     <col min="9" max="9" width="14.109375" style="2" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="15.109375" style="2" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="10.5546875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15.6640625" style="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.3">
@@ -1011,7 +1011,7 @@
         <v>1000177190024</v>
       </c>
       <c r="K3" s="1">
-        <v>46227</v>
+        <v>46077</v>
       </c>
       <c r="L3" s="2">
         <v>251912861288</v>
@@ -1175,7 +1175,7 @@
         <v>1000177190024</v>
       </c>
       <c r="K7" s="1">
-        <v>46227</v>
+        <v>46107</v>
       </c>
       <c r="L7" s="2">
         <v>251912861288</v>
@@ -1626,7 +1626,7 @@
         <v>1000177190024</v>
       </c>
       <c r="K18" s="1">
-        <v>46227</v>
+        <v>46293</v>
       </c>
       <c r="L18" s="2">
         <v>251912861288</v>
@@ -1954,7 +1954,7 @@
         <v>1000177190024</v>
       </c>
       <c r="K26" s="1">
-        <v>46227</v>
+        <v>46166</v>
       </c>
       <c r="L26" s="2">
         <v>251912861288</v>
@@ -2077,7 +2077,7 @@
         <v>1000177190024</v>
       </c>
       <c r="K29" s="1">
-        <v>46227</v>
+        <v>46198</v>
       </c>
       <c r="L29" s="2">
         <v>251912861288</v>

--- a/EGSA2025_short_loan.xlsx
+++ b/EGSA2025_short_loan.xlsx
@@ -85,6 +85,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
+  </numFmts>
   <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -562,10 +565,11 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="17" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -892,9 +896,9 @@
   <cols>
     <col min="2" max="2" width="12.44140625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="14.109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="18" style="3" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="10.5546875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="15.6640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.109375" style="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.3">
@@ -925,7 +929,7 @@
       <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="3" t="s">
         <v>9</v>
       </c>
       <c r="K1" t="s">
@@ -966,7 +970,7 @@
       <c r="I2" s="2">
         <v>1000724673337</v>
       </c>
-      <c r="J2" s="2">
+      <c r="J2" s="3">
         <v>1000289318236</v>
       </c>
       <c r="K2" s="1">
@@ -1007,7 +1011,7 @@
       <c r="I3" s="2">
         <v>1000724673337</v>
       </c>
-      <c r="J3" s="2">
+      <c r="J3" s="3">
         <v>1000177190024</v>
       </c>
       <c r="K3" s="1">
@@ -1048,7 +1052,7 @@
       <c r="I4" s="2">
         <v>1000724673337</v>
       </c>
-      <c r="J4" s="2">
+      <c r="J4" s="3">
         <v>1000272980423</v>
       </c>
       <c r="K4" s="1">
@@ -1089,7 +1093,7 @@
       <c r="I5" s="2">
         <v>1000724673337</v>
       </c>
-      <c r="J5" s="2">
+      <c r="J5" s="3">
         <v>1000496218101</v>
       </c>
       <c r="K5" s="1">
@@ -1130,7 +1134,7 @@
       <c r="I6" s="2">
         <v>1000724673337</v>
       </c>
-      <c r="J6" s="2">
+      <c r="J6" s="3">
         <v>1000378957161</v>
       </c>
       <c r="K6" s="1">
@@ -1171,7 +1175,7 @@
       <c r="I7" s="2">
         <v>1000724673337</v>
       </c>
-      <c r="J7" s="2">
+      <c r="J7" s="3">
         <v>1000177190024</v>
       </c>
       <c r="K7" s="1">
@@ -1212,7 +1216,7 @@
       <c r="I8" s="2">
         <v>1000724673337</v>
       </c>
-      <c r="J8" s="2">
+      <c r="J8" s="3">
         <v>1000531405424</v>
       </c>
       <c r="K8" s="1">
@@ -1253,7 +1257,7 @@
       <c r="I9" s="2">
         <v>1000724673337</v>
       </c>
-      <c r="J9" s="2">
+      <c r="J9" s="3">
         <v>1000553520502</v>
       </c>
       <c r="K9" s="1">
@@ -1294,7 +1298,7 @@
       <c r="I10" s="2">
         <v>1000724673337</v>
       </c>
-      <c r="J10" s="2">
+      <c r="J10" s="3">
         <v>1000289318236</v>
       </c>
       <c r="K10" s="1">
@@ -1335,7 +1339,7 @@
       <c r="I11" s="2">
         <v>1000724673337</v>
       </c>
-      <c r="J11" s="2">
+      <c r="J11" s="3">
         <v>1000263206022</v>
       </c>
       <c r="K11" s="1">
@@ -1376,7 +1380,7 @@
       <c r="I12" s="2">
         <v>1000724673337</v>
       </c>
-      <c r="J12" s="2">
+      <c r="J12" s="3">
         <v>1000094217214</v>
       </c>
       <c r="K12" s="1">
@@ -1417,7 +1421,7 @@
       <c r="I13" s="2">
         <v>1000727672676</v>
       </c>
-      <c r="J13" s="2">
+      <c r="J13" s="3">
         <v>1000657475649</v>
       </c>
       <c r="K13" s="1">
@@ -1458,7 +1462,7 @@
       <c r="I14" s="2">
         <v>1000724673337</v>
       </c>
-      <c r="J14" s="2">
+      <c r="J14" s="3">
         <v>1000016351087</v>
       </c>
       <c r="K14" s="1">
@@ -1499,7 +1503,7 @@
       <c r="I15" s="2">
         <v>1000724673337</v>
       </c>
-      <c r="J15" s="2">
+      <c r="J15" s="3">
         <v>1000205376635</v>
       </c>
       <c r="K15" s="1">
@@ -1540,7 +1544,7 @@
       <c r="I16" s="2">
         <v>1000724673337</v>
       </c>
-      <c r="J16" s="2">
+      <c r="J16" s="3">
         <v>1000272980423</v>
       </c>
       <c r="K16" s="1">
@@ -1581,7 +1585,7 @@
       <c r="I17" s="2">
         <v>1000724673337</v>
       </c>
-      <c r="J17" s="2">
+      <c r="J17" s="3">
         <v>1000378957161</v>
       </c>
       <c r="K17" s="1">
@@ -1622,7 +1626,7 @@
       <c r="I18" s="2">
         <v>1000724673337</v>
       </c>
-      <c r="J18" s="2">
+      <c r="J18" s="3">
         <v>1000177190024</v>
       </c>
       <c r="K18" s="1">
@@ -1663,7 +1667,7 @@
       <c r="I19" s="2">
         <v>1000724673337</v>
       </c>
-      <c r="J19" s="2">
+      <c r="J19" s="3">
         <v>1000496218101</v>
       </c>
       <c r="K19" s="1">
@@ -1704,7 +1708,7 @@
       <c r="I20" s="2">
         <v>1000724673337</v>
       </c>
-      <c r="J20" s="2">
+      <c r="J20" s="3">
         <v>1000531405424</v>
       </c>
       <c r="K20" s="1">
@@ -1745,7 +1749,7 @@
       <c r="I21" s="2">
         <v>1000724673337</v>
       </c>
-      <c r="J21" s="2">
+      <c r="J21" s="3">
         <v>1000272980423</v>
       </c>
       <c r="K21" s="1">
@@ -1786,7 +1790,7 @@
       <c r="I22" s="2">
         <v>1000724673337</v>
       </c>
-      <c r="J22" s="2">
+      <c r="J22" s="3">
         <v>1000031177433</v>
       </c>
       <c r="K22" s="1">
@@ -1827,7 +1831,7 @@
       <c r="I23" s="2">
         <v>1000724673337</v>
       </c>
-      <c r="J23" s="2">
+      <c r="J23" s="3">
         <v>1000553520502</v>
       </c>
       <c r="K23" s="1">
@@ -1868,7 +1872,7 @@
       <c r="I24" s="2">
         <v>1000724673337</v>
       </c>
-      <c r="J24" s="2">
+      <c r="J24" s="3">
         <v>1000263206022</v>
       </c>
       <c r="K24" s="1">
@@ -1909,7 +1913,7 @@
       <c r="I25" s="2">
         <v>1000724673337</v>
       </c>
-      <c r="J25" s="2">
+      <c r="J25" s="3">
         <v>1000289318236</v>
       </c>
       <c r="K25" s="1">
@@ -1950,7 +1954,7 @@
       <c r="I26" s="2">
         <v>1000724673337</v>
       </c>
-      <c r="J26" s="2">
+      <c r="J26" s="3">
         <v>1000177190024</v>
       </c>
       <c r="K26" s="1">
@@ -1991,7 +1995,7 @@
       <c r="I27" s="2">
         <v>1000724673337</v>
       </c>
-      <c r="J27" s="2">
+      <c r="J27" s="3">
         <v>10001490488816</v>
       </c>
       <c r="K27" s="1">
@@ -2032,7 +2036,7 @@
       <c r="I28" s="2">
         <v>1000724673337</v>
       </c>
-      <c r="J28" s="2">
+      <c r="J28" s="3">
         <v>1000016351087</v>
       </c>
       <c r="K28" s="1">
@@ -2073,7 +2077,7 @@
       <c r="I29" s="2">
         <v>1000724673337</v>
       </c>
-      <c r="J29" s="2">
+      <c r="J29" s="3">
         <v>1000177190024</v>
       </c>
       <c r="K29" s="1">
@@ -2114,7 +2118,7 @@
       <c r="I30" s="2">
         <v>1000724673337</v>
       </c>
-      <c r="J30" s="2">
+      <c r="J30" s="3">
         <v>1000205376635</v>
       </c>
       <c r="K30" s="1">
@@ -2155,17 +2159,17 @@
       <c r="I31" s="2">
         <v>1000724673337</v>
       </c>
-      <c r="J31" s="2">
+      <c r="J31" s="3">
         <v>1000531405424</v>
       </c>
       <c r="K31" s="1">
-        <v>46237</v>
+        <v>46235</v>
       </c>
       <c r="L31" s="2">
         <v>251947763811</v>
       </c>
       <c r="M31" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.3">
@@ -2196,7 +2200,7 @@
       <c r="I32" s="2">
         <v>1000724673337</v>
       </c>
-      <c r="J32" s="2">
+      <c r="J32" s="3">
         <v>1000289318236</v>
       </c>
       <c r="K32" s="1">
@@ -2237,7 +2241,7 @@
       <c r="I33" s="2">
         <v>1000724673337</v>
       </c>
-      <c r="J33" s="2">
+      <c r="J33" s="3">
         <v>1000289318236</v>
       </c>
       <c r="K33" s="1">
@@ -2278,7 +2282,7 @@
       <c r="I34" s="2">
         <v>1000724673337</v>
       </c>
-      <c r="J34" s="2">
+      <c r="J34" s="3">
         <v>1000553520502</v>
       </c>
       <c r="K34" s="1">
@@ -2319,7 +2323,7 @@
       <c r="I35" s="2">
         <v>1000724673337</v>
       </c>
-      <c r="J35" s="2">
+      <c r="J35" s="3">
         <v>1000177190024</v>
       </c>
       <c r="K35" s="1">
@@ -2360,7 +2364,7 @@
       <c r="I36" s="2">
         <v>1000724673337</v>
       </c>
-      <c r="J36" s="2">
+      <c r="J36" s="3">
         <v>1000289318236</v>
       </c>
       <c r="K36" s="1">
@@ -2401,7 +2405,7 @@
       <c r="I37" s="2">
         <v>1000724673337</v>
       </c>
-      <c r="J37" s="2">
+      <c r="J37" s="3">
         <v>1000263206022</v>
       </c>
       <c r="K37" s="1">
@@ -2442,17 +2446,17 @@
       <c r="I38" s="2">
         <v>1000724673337</v>
       </c>
-      <c r="J38" s="2">
+      <c r="J38" s="3">
         <v>1000205376635</v>
       </c>
       <c r="K38" s="1">
-        <v>46233</v>
+        <v>46232</v>
       </c>
       <c r="L38" s="2">
         <v>251922956646</v>
       </c>
       <c r="M38" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.3">
@@ -2483,17 +2487,17 @@
       <c r="I39" s="2">
         <v>1000724673337</v>
       </c>
-      <c r="J39" s="2">
+      <c r="J39" s="3">
         <v>1000496218101</v>
       </c>
       <c r="K39" s="1">
-        <v>46233</v>
+        <v>46232</v>
       </c>
       <c r="L39" s="2">
         <v>251977677737</v>
       </c>
       <c r="M39" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.3">
@@ -2524,7 +2528,7 @@
       <c r="I40" s="2">
         <v>1000724673337</v>
       </c>
-      <c r="J40" s="2">
+      <c r="J40" s="3">
         <v>1000016981088</v>
       </c>
       <c r="K40" s="1">
@@ -2565,7 +2569,7 @@
       <c r="I41" s="2">
         <v>1000724673337</v>
       </c>
-      <c r="J41" s="2">
+      <c r="J41" s="3">
         <v>1000016351087</v>
       </c>
       <c r="K41" s="1">
@@ -2606,7 +2610,7 @@
       <c r="I42" s="2">
         <v>1000724673337</v>
       </c>
-      <c r="J42" s="2">
+      <c r="J42" s="3">
         <v>1000548538797</v>
       </c>
       <c r="K42" s="1">
@@ -2647,7 +2651,7 @@
       <c r="I43" s="2">
         <v>1000724673337</v>
       </c>
-      <c r="J43" s="2">
+      <c r="J43" s="3">
         <v>1000657475649</v>
       </c>
       <c r="K43" s="1">

--- a/EGSA2025_short_loan.xlsx
+++ b/EGSA2025_short_loan.xlsx
@@ -85,9 +85,6 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
-  </numFmts>
   <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -565,11 +562,10 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="17" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -896,7 +892,7 @@
   <cols>
     <col min="2" max="2" width="12.44140625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="14.109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="18" style="3" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.109375" style="2" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="10.5546875" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="13.109375" style="2" bestFit="1" customWidth="1"/>
   </cols>
@@ -929,7 +925,7 @@
       <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K1" t="s">
@@ -970,7 +966,7 @@
       <c r="I2" s="2">
         <v>1000724673337</v>
       </c>
-      <c r="J2" s="3">
+      <c r="J2" s="2">
         <v>1000289318236</v>
       </c>
       <c r="K2" s="1">
@@ -1011,7 +1007,7 @@
       <c r="I3" s="2">
         <v>1000724673337</v>
       </c>
-      <c r="J3" s="3">
+      <c r="J3" s="2">
         <v>1000177190024</v>
       </c>
       <c r="K3" s="1">
@@ -1052,7 +1048,7 @@
       <c r="I4" s="2">
         <v>1000724673337</v>
       </c>
-      <c r="J4" s="3">
+      <c r="J4" s="2">
         <v>1000272980423</v>
       </c>
       <c r="K4" s="1">
@@ -1093,7 +1089,7 @@
       <c r="I5" s="2">
         <v>1000724673337</v>
       </c>
-      <c r="J5" s="3">
+      <c r="J5" s="2">
         <v>1000496218101</v>
       </c>
       <c r="K5" s="1">
@@ -1134,7 +1130,7 @@
       <c r="I6" s="2">
         <v>1000724673337</v>
       </c>
-      <c r="J6" s="3">
+      <c r="J6" s="2">
         <v>1000378957161</v>
       </c>
       <c r="K6" s="1">
@@ -1175,7 +1171,7 @@
       <c r="I7" s="2">
         <v>1000724673337</v>
       </c>
-      <c r="J7" s="3">
+      <c r="J7" s="2">
         <v>1000177190024</v>
       </c>
       <c r="K7" s="1">
@@ -1216,7 +1212,7 @@
       <c r="I8" s="2">
         <v>1000724673337</v>
       </c>
-      <c r="J8" s="3">
+      <c r="J8" s="2">
         <v>1000531405424</v>
       </c>
       <c r="K8" s="1">
@@ -1257,7 +1253,7 @@
       <c r="I9" s="2">
         <v>1000724673337</v>
       </c>
-      <c r="J9" s="3">
+      <c r="J9" s="2">
         <v>1000553520502</v>
       </c>
       <c r="K9" s="1">
@@ -1298,7 +1294,7 @@
       <c r="I10" s="2">
         <v>1000724673337</v>
       </c>
-      <c r="J10" s="3">
+      <c r="J10" s="2">
         <v>1000289318236</v>
       </c>
       <c r="K10" s="1">
@@ -1339,7 +1335,7 @@
       <c r="I11" s="2">
         <v>1000724673337</v>
       </c>
-      <c r="J11" s="3">
+      <c r="J11" s="2">
         <v>1000263206022</v>
       </c>
       <c r="K11" s="1">
@@ -1380,7 +1376,7 @@
       <c r="I12" s="2">
         <v>1000724673337</v>
       </c>
-      <c r="J12" s="3">
+      <c r="J12" s="2">
         <v>1000094217214</v>
       </c>
       <c r="K12" s="1">
@@ -1421,7 +1417,7 @@
       <c r="I13" s="2">
         <v>1000727672676</v>
       </c>
-      <c r="J13" s="3">
+      <c r="J13" s="2">
         <v>1000657475649</v>
       </c>
       <c r="K13" s="1">
@@ -1462,7 +1458,7 @@
       <c r="I14" s="2">
         <v>1000724673337</v>
       </c>
-      <c r="J14" s="3">
+      <c r="J14" s="2">
         <v>1000016351087</v>
       </c>
       <c r="K14" s="1">
@@ -1503,7 +1499,7 @@
       <c r="I15" s="2">
         <v>1000724673337</v>
       </c>
-      <c r="J15" s="3">
+      <c r="J15" s="2">
         <v>1000205376635</v>
       </c>
       <c r="K15" s="1">
@@ -1544,7 +1540,7 @@
       <c r="I16" s="2">
         <v>1000724673337</v>
       </c>
-      <c r="J16" s="3">
+      <c r="J16" s="2">
         <v>1000272980423</v>
       </c>
       <c r="K16" s="1">
@@ -1585,7 +1581,7 @@
       <c r="I17" s="2">
         <v>1000724673337</v>
       </c>
-      <c r="J17" s="3">
+      <c r="J17" s="2">
         <v>1000378957161</v>
       </c>
       <c r="K17" s="1">
@@ -1626,7 +1622,7 @@
       <c r="I18" s="2">
         <v>1000724673337</v>
       </c>
-      <c r="J18" s="3">
+      <c r="J18" s="2">
         <v>1000177190024</v>
       </c>
       <c r="K18" s="1">
@@ -1667,7 +1663,7 @@
       <c r="I19" s="2">
         <v>1000724673337</v>
       </c>
-      <c r="J19" s="3">
+      <c r="J19" s="2">
         <v>1000496218101</v>
       </c>
       <c r="K19" s="1">
@@ -1708,7 +1704,7 @@
       <c r="I20" s="2">
         <v>1000724673337</v>
       </c>
-      <c r="J20" s="3">
+      <c r="J20" s="2">
         <v>1000531405424</v>
       </c>
       <c r="K20" s="1">
@@ -1749,7 +1745,7 @@
       <c r="I21" s="2">
         <v>1000724673337</v>
       </c>
-      <c r="J21" s="3">
+      <c r="J21" s="2">
         <v>1000272980423</v>
       </c>
       <c r="K21" s="1">
@@ -1790,7 +1786,7 @@
       <c r="I22" s="2">
         <v>1000724673337</v>
       </c>
-      <c r="J22" s="3">
+      <c r="J22" s="2">
         <v>1000031177433</v>
       </c>
       <c r="K22" s="1">
@@ -1831,7 +1827,7 @@
       <c r="I23" s="2">
         <v>1000724673337</v>
       </c>
-      <c r="J23" s="3">
+      <c r="J23" s="2">
         <v>1000553520502</v>
       </c>
       <c r="K23" s="1">
@@ -1872,7 +1868,7 @@
       <c r="I24" s="2">
         <v>1000724673337</v>
       </c>
-      <c r="J24" s="3">
+      <c r="J24" s="2">
         <v>1000263206022</v>
       </c>
       <c r="K24" s="1">
@@ -1913,7 +1909,7 @@
       <c r="I25" s="2">
         <v>1000724673337</v>
       </c>
-      <c r="J25" s="3">
+      <c r="J25" s="2">
         <v>1000289318236</v>
       </c>
       <c r="K25" s="1">
@@ -1954,7 +1950,7 @@
       <c r="I26" s="2">
         <v>1000724673337</v>
       </c>
-      <c r="J26" s="3">
+      <c r="J26" s="2">
         <v>1000177190024</v>
       </c>
       <c r="K26" s="1">
@@ -1995,7 +1991,7 @@
       <c r="I27" s="2">
         <v>1000724673337</v>
       </c>
-      <c r="J27" s="3">
+      <c r="J27" s="2">
         <v>10001490488816</v>
       </c>
       <c r="K27" s="1">
@@ -2036,7 +2032,7 @@
       <c r="I28" s="2">
         <v>1000724673337</v>
       </c>
-      <c r="J28" s="3">
+      <c r="J28" s="2">
         <v>1000016351087</v>
       </c>
       <c r="K28" s="1">
@@ -2077,7 +2073,7 @@
       <c r="I29" s="2">
         <v>1000724673337</v>
       </c>
-      <c r="J29" s="3">
+      <c r="J29" s="2">
         <v>1000177190024</v>
       </c>
       <c r="K29" s="1">
@@ -2118,7 +2114,7 @@
       <c r="I30" s="2">
         <v>1000724673337</v>
       </c>
-      <c r="J30" s="3">
+      <c r="J30" s="2">
         <v>1000205376635</v>
       </c>
       <c r="K30" s="1">
@@ -2159,7 +2155,7 @@
       <c r="I31" s="2">
         <v>1000724673337</v>
       </c>
-      <c r="J31" s="3">
+      <c r="J31" s="2">
         <v>1000531405424</v>
       </c>
       <c r="K31" s="1">
@@ -2200,7 +2196,7 @@
       <c r="I32" s="2">
         <v>1000724673337</v>
       </c>
-      <c r="J32" s="3">
+      <c r="J32" s="2">
         <v>1000289318236</v>
       </c>
       <c r="K32" s="1">
@@ -2241,7 +2237,7 @@
       <c r="I33" s="2">
         <v>1000724673337</v>
       </c>
-      <c r="J33" s="3">
+      <c r="J33" s="2">
         <v>1000289318236</v>
       </c>
       <c r="K33" s="1">
@@ -2282,17 +2278,17 @@
       <c r="I34" s="2">
         <v>1000724673337</v>
       </c>
-      <c r="J34" s="3">
+      <c r="J34" s="2">
         <v>1000553520502</v>
       </c>
       <c r="K34" s="1">
-        <v>46257</v>
+        <v>46255</v>
       </c>
       <c r="L34" s="2">
         <v>251954846351</v>
       </c>
       <c r="M34" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.3">
@@ -2323,7 +2319,7 @@
       <c r="I35" s="2">
         <v>1000724673337</v>
       </c>
-      <c r="J35" s="3">
+      <c r="J35" s="2">
         <v>1000177190024</v>
       </c>
       <c r="K35" s="1">
@@ -2364,7 +2360,7 @@
       <c r="I36" s="2">
         <v>1000724673337</v>
       </c>
-      <c r="J36" s="3">
+      <c r="J36" s="2">
         <v>1000289318236</v>
       </c>
       <c r="K36" s="1">
@@ -2405,7 +2401,7 @@
       <c r="I37" s="2">
         <v>1000724673337</v>
       </c>
-      <c r="J37" s="3">
+      <c r="J37" s="2">
         <v>1000263206022</v>
       </c>
       <c r="K37" s="1">
@@ -2446,7 +2442,7 @@
       <c r="I38" s="2">
         <v>1000724673337</v>
       </c>
-      <c r="J38" s="3">
+      <c r="J38" s="2">
         <v>1000205376635</v>
       </c>
       <c r="K38" s="1">
@@ -2487,7 +2483,7 @@
       <c r="I39" s="2">
         <v>1000724673337</v>
       </c>
-      <c r="J39" s="3">
+      <c r="J39" s="2">
         <v>1000496218101</v>
       </c>
       <c r="K39" s="1">
@@ -2528,7 +2524,7 @@
       <c r="I40" s="2">
         <v>1000724673337</v>
       </c>
-      <c r="J40" s="3">
+      <c r="J40" s="2">
         <v>1000016981088</v>
       </c>
       <c r="K40" s="1">
@@ -2569,7 +2565,7 @@
       <c r="I41" s="2">
         <v>1000724673337</v>
       </c>
-      <c r="J41" s="3">
+      <c r="J41" s="2">
         <v>1000016351087</v>
       </c>
       <c r="K41" s="1">
@@ -2610,7 +2606,7 @@
       <c r="I42" s="2">
         <v>1000724673337</v>
       </c>
-      <c r="J42" s="3">
+      <c r="J42" s="2">
         <v>1000548538797</v>
       </c>
       <c r="K42" s="1">
@@ -2651,7 +2647,7 @@
       <c r="I43" s="2">
         <v>1000724673337</v>
       </c>
-      <c r="J43" s="3">
+      <c r="J43" s="2">
         <v>1000657475649</v>
       </c>
       <c r="K43" s="1">

--- a/EGSA2025_short_loan.xlsx
+++ b/EGSA2025_short_loan.xlsx
@@ -891,6 +891,7 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.109375" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="14.109375" style="2" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="15.109375" style="2" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="10.5546875" bestFit="1" customWidth="1"/>
@@ -2405,13 +2406,13 @@
         <v>1000263206022</v>
       </c>
       <c r="K37" s="1">
-        <v>46261</v>
+        <v>46260</v>
       </c>
       <c r="L37" s="2">
         <v>251935869198</v>
       </c>
       <c r="M37" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.3">

--- a/EGSA2025_short_loan.xlsx
+++ b/EGSA2025_short_loan.xlsx
@@ -891,7 +891,6 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.109375" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="14.109375" style="2" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="15.109375" style="2" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="10.5546875" bestFit="1" customWidth="1"/>
@@ -2529,13 +2528,13 @@
         <v>1000016981088</v>
       </c>
       <c r="K40" s="1">
-        <v>46266</v>
+        <v>46265</v>
       </c>
       <c r="L40" s="2">
         <v>251902666362</v>
       </c>
       <c r="M40" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
     </row>
     <row r="41" spans="1:13" x14ac:dyDescent="0.3">

--- a/EGSA2025_short_loan.xlsx
+++ b/EGSA2025_short_loan.xlsx
@@ -2575,7 +2575,7 @@
         <v>251912356447</v>
       </c>
       <c r="M41" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
     </row>
     <row r="42" spans="1:13" x14ac:dyDescent="0.3">

--- a/EGSA2025_short_loan.xlsx
+++ b/EGSA2025_short_loan.xlsx
@@ -2569,7 +2569,7 @@
         <v>1000016351087</v>
       </c>
       <c r="K41" s="1">
-        <v>46267</v>
+        <v>46265</v>
       </c>
       <c r="L41" s="2">
         <v>251912356447</v>

--- a/EGSA2025_short_loan.xlsx
+++ b/EGSA2025_short_loan.xlsx
@@ -894,7 +894,7 @@
     <col min="9" max="9" width="14.109375" style="2" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="15.109375" style="2" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="10.5546875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15.6640625" style="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.3">
@@ -2569,7 +2569,7 @@
         <v>1000016351087</v>
       </c>
       <c r="K41" s="1">
-        <v>46265</v>
+        <v>46267</v>
       </c>
       <c r="L41" s="2">
         <v>251912356447</v>
@@ -2616,7 +2616,7 @@
         <v>251965224695</v>
       </c>
       <c r="M42" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.3">

--- a/EGSA2025_short_loan.xlsx
+++ b/EGSA2025_short_loan.xlsx
@@ -2610,7 +2610,7 @@
         <v>1000548538797</v>
       </c>
       <c r="K42" s="1">
-        <v>46268</v>
+        <v>46267</v>
       </c>
       <c r="L42" s="2">
         <v>251965224695</v>
